--- a/data/Bengaluru_Places_Catalog.xlsx
+++ b/data/Bengaluru_Places_Catalog.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Places" sheetId="1" r:id="R5a32c074996c4ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" r:id="R5fb4e6d8409a477d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Places" sheetId="1" r:id="R8098b521b5eb48c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" r:id="Ra6071c10ddf34507"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,12 +38,22 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF21483D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF21483D"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -63,7 +73,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -88,6 +98,8 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -96,7 +108,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BengaluruPlaces" displayName="BengaluruPlaces" ref="A1:L166" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BengaluruPlaces" displayName="BengaluruPlaces" ref="A1:L248" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Place name"/>
     <x:tableColumn id="2" name="Category"/>
@@ -315,12 +327,12 @@
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="72" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="64" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="70" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="72" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="54" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="54" hidden="0" customWidth="1"/>
@@ -328,40 +340,40 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="2" t="str">
+      <x:c r="A1" s="13" t="str">
         <x:v>Place name</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="str">
+      <x:c r="B1" s="13" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
+      <x:c r="C1" s="13" t="str">
         <x:v>Neighbourhood / area</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="str">
+      <x:c r="D1" s="13" t="str">
         <x:v>Description</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="str">
+      <x:c r="E1" s="13" t="str">
         <x:v>Mood fit (editorial)</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="str">
+      <x:c r="F1" s="13" t="str">
         <x:v>Ambience (editorial)</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="str">
+      <x:c r="G1" s="13" t="str">
         <x:v>Indicative pricing</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="str">
+      <x:c r="H1" s="13" t="str">
         <x:v>Pricing basis / caveat</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="str">
+      <x:c r="I1" s="13" t="str">
         <x:v>Qloo entity ID</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="str">
+      <x:c r="J1" s="13" t="str">
         <x:v>Research source</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="str">
+      <x:c r="K1" s="13" t="str">
         <x:v>Venue lookup</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="str">
+      <x:c r="L1" s="13" t="str">
         <x:v>Verification status</x:v>
       </x:c>
     </x:row>
@@ -3547,10 +3559,10 @@
         <x:v>Cafe combined with an independent bookstore; reading and quiet-work cues are venue-described.</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Quiet focus, reading, solo work</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Bookstore-cafe with dedicated work facilities; weekday hours are a better calm-work bet.</x:v>
       </x:c>
       <x:c r="G90" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3583,10 +3595,10 @@
         <x:v>Art-led cafe in a relaxed setting with a courtyard feel.</x:v>
       </x:c>
       <x:c r="E91" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Calm, creative, slow lunch</x:v>
       </x:c>
       <x:c r="F91" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Courtyard bungalow with rotating local art; no loud music is reported in a current guide.</x:v>
       </x:c>
       <x:c r="G91" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3596,7 +3608,7 @@
       </x:c>
       <x:c r="I91" s="4" t="str"/>
       <x:c r="J91" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
       </x:c>
       <x:c r="K91" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Dyu%20Art%20Cafe%2C%20Koramangala%205th%20Block%2C%20Bengaluru</x:v>
@@ -3619,10 +3631,10 @@
         <x:v>Specialty coffee chain with many Bengaluru branches; select the nearest branch.</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Coffee ritual, focus, casual meet-up</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Branch-dependent chain; guide reports plugs and Wi-Fi at many stores. Weekends can be busy.</x:v>
       </x:c>
       <x:c r="G92" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3632,7 +3644,7 @@
       </x:c>
       <x:c r="I92" s="4" t="str"/>
       <x:c r="J92" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://stores.thirdwavecoffeeroasters.com/location/bengaluru</x:v>
       </x:c>
       <x:c r="K92" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Third%20Wave%20Coffee%20Roasters%2C%20Multiple%20neighbourhoods%2C%20Bengaluru</x:v>
@@ -3655,10 +3667,10 @@
         <x:v>Specialty coffee and cafe menu across several city locations.</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Coffee tasting, short focused stop</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Indiranagar outlet is small; source guide recommends coffee rather than a long laptop session.</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3668,7 +3680,7 @@
       </x:c>
       <x:c r="I93" s="4" t="str"/>
       <x:c r="J93" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://bluetokaicoffee.com/</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Blue%20Tokai%20Coffee%20Roasters%2C%20Multiple%20neighbourhoods%2C%20Bengaluru</x:v>
@@ -3691,10 +3703,10 @@
         <x:v>Coffee-focused cafe showcasing Araku Valley beans and a contemporary interior.</x:v>
       </x:c>
       <x:c r="E94" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Coffee exploration, design, quiet catch-up</x:v>
       </x:c>
       <x:c r="F94" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Two-storey specialty coffee cafe with roastery and a small bookstore; can be a premium visit.</x:v>
       </x:c>
       <x:c r="G94" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3704,7 +3716,7 @@
       </x:c>
       <x:c r="I94" s="4" t="str"/>
       <x:c r="J94" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://www.arakucoffee.in/</x:v>
       </x:c>
       <x:c r="K94" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Araku%20Coffee%2C%20Indiranagar%2C%20Bengaluru</x:v>
@@ -3799,10 +3811,10 @@
         <x:v>Independent bookstore with a cafe and reading-oriented atmosphere.</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Reading, calm solo time, gentle work</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Rooftop bungalow bookstore-library-cafe with tree views, Wi-Fi and about 30 seats reported by LBB.</x:v>
       </x:c>
       <x:c r="G97" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3812,7 +3824,7 @@
       </x:c>
       <x:c r="I97" s="4" t="str"/>
       <x:c r="J97" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://lbb.in/bangalore/champaca-cafe-bookstore-library-vasanth-nagar/</x:v>
       </x:c>
       <x:c r="K97" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Champaca%20Bookstore%20%26%20Cafe%2C%20Vasanth%20Nagar%2C%20Bengaluru</x:v>
@@ -3835,10 +3847,10 @@
         <x:v>Central coffee stop on the pedestrian-friendly Church Street stretch.</x:v>
       </x:c>
       <x:c r="E98" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Coffee-focused work, bright reset</x:v>
       </x:c>
       <x:c r="F98" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Light-filled work-cafe cues with Wi-Fi and power outlets reported; confirm branch facilities.</x:v>
       </x:c>
       <x:c r="G98" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3848,7 +3860,7 @@
       </x:c>
       <x:c r="I98" s="4" t="str"/>
       <x:c r="J98" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
       </x:c>
       <x:c r="K98" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Matteo%20Coffea%2C%20Church%20Street%2C%20Bengaluru</x:v>
@@ -3907,10 +3919,10 @@
         <x:v>Pay-by-time cafe concept with work and games; current pricing and format vary by branch.</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Long stay, games, social work</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Pay-by-time concept with activities; not a silent cafe, and rules/pricing vary by branch.</x:v>
       </x:c>
       <x:c r="G100" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -3920,7 +3932,7 @@
       </x:c>
       <x:c r="I100" s="4" t="str"/>
       <x:c r="J100" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
       </x:c>
       <x:c r="K100" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Dialogues%20Cafe%2C%20Koramangala%20%2F%20multiple%20branches%2C%20Bengaluru</x:v>
@@ -4015,10 +4027,10 @@
         <x:v>Coffee roastery-cafe with a craft-led, relaxed feel.</x:v>
       </x:c>
       <x:c r="E103" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Specialty coffee, curious tasting</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Coffee-roastery identity and experimental brews; seating and noise depend on branch.</x:v>
       </x:c>
       <x:c r="G103" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -4028,7 +4040,7 @@
       </x:c>
       <x:c r="I103" s="4" t="str"/>
       <x:c r="J103" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
       </x:c>
       <x:c r="K103" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Maverick%20%26%20Farmer%20Coffee%2C%20Jayanagar%20%2F%20other%20branches%2C%20Bengaluru</x:v>
@@ -4051,10 +4063,10 @@
         <x:v>Cafe and coffee stop associated with laptop-friendly visits; verify branch details.</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Laptop session, coffee break</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Work-friendly reputation is branch/time dependent; confirm Wi-Fi and outlet access.</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -4064,7 +4076,7 @@
       </x:c>
       <x:c r="I104" s="4" t="str"/>
       <x:c r="J104" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Coffee%20Brewery%2C%20Indiranagar%2C%20Bengaluru</x:v>
@@ -4087,10 +4099,10 @@
         <x:v>Neighbourhood cafe with garden and relaxed brunch cues; verify current operation.</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Garden pause, slow brunch</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Garden/greenery cues; check current opening and crowd before planning a quiet visit.</x:v>
       </x:c>
       <x:c r="G105" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -4100,7 +4112,7 @@
       </x:c>
       <x:c r="I105" s="4" t="str"/>
       <x:c r="J105" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K105" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Huvu%20Cafe%2C%20Indiranagar%2C%20Bengaluru</x:v>
@@ -4303,10 +4315,10 @@
         <x:v>Garden-style restaurant and cafe with greenery and outdoor seating.</x:v>
       </x:c>
       <x:c r="E111" s="4" t="str">
-        <x:v>Slow down, focus, catch up</x:v>
+        <x:v>Garden dining, relaxed catch-up</x:v>
       </x:c>
       <x:c r="F111" s="4" t="str">
-        <x:v>Cafe atmospheres vary by branch, time and crowd; laptop suitability is not guaranteed</x:v>
+        <x:v>Green outdoor setting; it is a restaurant-cafe and may be lively at peak dining hours.</x:v>
       </x:c>
       <x:c r="G111" s="4" t="str">
         <x:v>₹250–₹1,000 per person (broad estimate)</x:v>
@@ -4316,7 +4328,7 @@
       </x:c>
       <x:c r="I111" s="4" t="str"/>
       <x:c r="J111" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
       </x:c>
       <x:c r="K111" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gawky%20Goose%2C%20Whitefield%2C%20Bengaluru</x:v>
@@ -4352,7 +4364,7 @@
       </x:c>
       <x:c r="I112" s="4" t="str"/>
       <x:c r="J112" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://theobroma.in/</x:v>
       </x:c>
       <x:c r="K112" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Theobroma%2C%20Multiple%20neighbourhoods%2C%20Bengaluru</x:v>
@@ -4388,7 +4400,7 @@
       </x:c>
       <x:c r="I113" s="4" t="str"/>
       <x:c r="J113" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/experiences/paper-pie-cafe/</x:v>
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
       </x:c>
       <x:c r="K113" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=Caf%C3%A9%20Noir%2C%20UB%20City%2C%20Bengaluru</x:v>
@@ -4435,1880 +4447,4832 @@
     </x:row>
     <x:row r="115" ht="54" customHeight="1">
       <x:c r="A115" s="4" t="str">
-        <x:v>PLaY Arena</x:v>
+        <x:v>Got Tea</x:v>
       </x:c>
       <x:c r="B115" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C115" s="4" t="str">
-        <x:v>Kasavanahalli / Sarjapur Road</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D115" s="4" t="str">
-        <x:v>Multi-activity venue with go-karting, bowling, paintball, climbing and other games.</x:v>
+        <x:v>Tea and matcha stop with trees and coworking facilities listed in current city guides.</x:v>
       </x:c>
       <x:c r="E115" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Work break, tea mood, green pause</x:v>
       </x:c>
       <x:c r="F115" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Tree-adjacent setting; coworking is listed, but crowd/noise vary by hour.</x:v>
       </x:c>
       <x:c r="G115" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹150–₹600</x:v>
       </x:c>
       <x:c r="H115" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I115" s="4" t="str"/>
       <x:c r="J115" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K115" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=PLaY%20Arena%2C%20Kasavanahalli%20%2F%20Sarjapur%20Road%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Got%20Tea%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L115" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="54" customHeight="1">
       <x:c r="A116" s="4" t="str">
-        <x:v>Torq03</x:v>
+        <x:v>The Revolver Club</x:v>
       </x:c>
       <x:c r="B116" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C116" s="4" t="str">
-        <x:v>Marathahalli</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D116" s="4" t="str">
-        <x:v>Entertainment venue with bowling and indoor games; check current activity lineup.</x:v>
+        <x:v>Vinyl and vintage-watch store with a cafe element for a browse-and-coffee visit.</x:v>
       </x:c>
       <x:c r="E116" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Browse, music-minded, curious</x:v>
       </x:c>
       <x:c r="F116" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Retail-meets-cafe; more exploratory than a guaranteed quiet work spot.</x:v>
       </x:c>
       <x:c r="G116" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹900</x:v>
       </x:c>
       <x:c r="H116" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I116" s="4" t="str"/>
       <x:c r="J116" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K116" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Torq03%2C%20Marathahalli%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Revolver%20Club%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L116" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="54" customHeight="1">
       <x:c r="A117" s="4" t="str">
-        <x:v>Loco Bear</x:v>
+        <x:v>Coffee Angadi</x:v>
       </x:c>
       <x:c r="B117" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C117" s="4" t="str">
-        <x:v>Koramangala</x:v>
+        <x:v>Jayanagar</x:v>
       </x:c>
       <x:c r="D117" s="4" t="str">
-        <x:v>Indoor entertainment hub with bowling and games; verify current activities and timings.</x:v>
+        <x:v>Neighbourhood coffee shop and quick pause in Jayanagar 9th Block.</x:v>
       </x:c>
       <x:c r="E117" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Simple, familiar, low-key</x:v>
       </x:c>
       <x:c r="F117" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Local coffee-shop feel; seating and quietness need branch check.</x:v>
       </x:c>
       <x:c r="G117" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹50–₹300</x:v>
       </x:c>
       <x:c r="H117" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I117" s="4" t="str"/>
       <x:c r="J117" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K117" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Loco%20Bear%2C%20Koramangala%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Coffee%20Angadi%2C%20Jayanagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L117" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="54" customHeight="1">
       <x:c r="A118" s="4" t="str">
-        <x:v>The Grid</x:v>
+        <x:v>FLAX Cafe</x:v>
       </x:c>
       <x:c r="B118" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C118" s="4" t="str">
-        <x:v>Koramangala</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D118" s="4" t="str">
-        <x:v>Gaming arena offering bowling, laser tag and VR-style group activities.</x:v>
+        <x:v>Cafe with a health-conscious menu and bowls alongside coffee.</x:v>
       </x:c>
       <x:c r="E118" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Light, restorative, slow</x:v>
       </x:c>
       <x:c r="F118" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Contemporary cafe; visit off-peak for a calmer table.</x:v>
       </x:c>
       <x:c r="G118" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹300–₹900</x:v>
       </x:c>
       <x:c r="H118" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I118" s="4" t="str"/>
       <x:c r="J118" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K118" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Grid%2C%20Koramangala%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=FLAX%20Cafe%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L118" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="54" customHeight="1">
       <x:c r="A119" s="4" t="str">
-        <x:v>Amoeba</x:v>
+        <x:v>L81 Cafe</x:v>
       </x:c>
       <x:c r="B119" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C119" s="4" t="str">
-        <x:v>Brigade Road / branches</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D119" s="4" t="str">
-        <x:v>Bowling and arcade games in a mall setting; branch offerings vary.</x:v>
+        <x:v>Greenery-forward cafe with food and a relaxed neighbourhood setting.</x:v>
       </x:c>
       <x:c r="E119" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Cozy, nature-leaning, easygoing</x:v>
       </x:c>
       <x:c r="F119" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Trees and greenery are noted; check current seating and pet/cat details.</x:v>
       </x:c>
       <x:c r="G119" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H119" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I119" s="4" t="str"/>
       <x:c r="J119" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K119" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Amoeba%2C%20Brigade%20Road%20%2F%20branches%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=L81%20Cafe%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L119" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="54" customHeight="1">
       <x:c r="A120" s="4" t="str">
-        <x:v>Smaaash</x:v>
+        <x:v>Toastid Co.</x:v>
       </x:c>
       <x:c r="B120" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C120" s="4" t="str">
-        <x:v>Phoenix Marketcity / branch to confirm</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D120" s="4" t="str">
-        <x:v>Arcade and simulation games; confirm current Bengaluru location and activities.</x:v>
+        <x:v>Breakfast-and-coffee cafe known in local listings for its morning menu.</x:v>
       </x:c>
       <x:c r="E120" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Gentle start, comfort, brunch</x:v>
       </x:c>
       <x:c r="F120" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Breakfast-focused and likely busier at brunch; early weekday visit may be quieter.</x:v>
       </x:c>
       <x:c r="G120" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H120" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I120" s="4" t="str"/>
       <x:c r="J120" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K120" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Smaaash%2C%20Phoenix%20Marketcity%20%2F%20branch%20to%20confirm%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Toastid%20Co.%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L120" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="54" customHeight="1">
       <x:c r="A121" s="4" t="str">
-        <x:v>Snow City</x:v>
+        <x:v>Mathas Coffee</x:v>
       </x:c>
       <x:c r="B121" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C121" s="4" t="str">
-        <x:v>Jayamahal</x:v>
+        <x:v>Jayanagar</x:v>
       </x:c>
       <x:c r="D121" s="4" t="str">
-        <x:v>Indoor snow park experience; check sessions, clothing rules and current ticket packages.</x:v>
+        <x:v>Simple local coffee stop with very budget-conscious coffee options reported.</x:v>
       </x:c>
       <x:c r="E121" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Simple, budget, familiar</x:v>
       </x:c>
       <x:c r="F121" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>No-frills local stop; seating and service style may be limited.</x:v>
       </x:c>
       <x:c r="G121" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹30–₹250</x:v>
       </x:c>
       <x:c r="H121" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I121" s="4" t="str"/>
       <x:c r="J121" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K121" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Snow%20City%2C%20Jayamahal%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Mathas%20Coffee%2C%20Jayanagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L121" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="54" customHeight="1">
       <x:c r="A122" s="4" t="str">
-        <x:v>Wonderla Bengaluru</x:v>
+        <x:v>Chindalur’s Cafe</x:v>
       </x:c>
       <x:c r="B122" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C122" s="4" t="str">
-        <x:v>Mysore Road outskirts</x:v>
+        <x:v>Jayanagar</x:v>
       </x:c>
       <x:c r="D122" s="4" t="str">
-        <x:v>Large amusement and water park with rides; plan for a full day and check ticket calendar.</x:v>
+        <x:v>Small cafe/tiffin stop known for idli and South Indian comfort food.</x:v>
       </x:c>
       <x:c r="E122" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Comforting, local, unpretentious</x:v>
       </x:c>
       <x:c r="F122" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Simple neighbourhood cafe; best for a quick, easy meal.</x:v>
       </x:c>
       <x:c r="G122" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹50–₹350</x:v>
       </x:c>
       <x:c r="H122" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I122" s="4" t="str"/>
       <x:c r="J122" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K122" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Wonderla%20Bengaluru%2C%20Mysore%20Road%20outskirts%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Chindalur%E2%80%99s%20Cafe%2C%20Jayanagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L122" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="54" customHeight="1">
       <x:c r="A123" s="4" t="str">
-        <x:v>Climb Central Bengaluru</x:v>
+        <x:v>Twilight – T’ Coffee House</x:v>
       </x:c>
       <x:c r="B123" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C123" s="4" t="str">
-        <x:v>Marathahalli</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D123" s="4" t="str">
-        <x:v>Indoor climbing gym for bouldering and rope climbing; check induction requirements.</x:v>
+        <x:v>Coffee house noted for iced and hot coffee in a tree-lined setting.</x:v>
       </x:c>
       <x:c r="E123" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Calm, cozy, coffee-first</x:v>
       </x:c>
       <x:c r="F123" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Under-tree setting is reported; check current crowd levels.</x:v>
       </x:c>
       <x:c r="G123" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹150–₹600</x:v>
       </x:c>
       <x:c r="H123" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I123" s="4" t="str"/>
       <x:c r="J123" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K123" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Climb%20Central%20Bengaluru%2C%20Marathahalli%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Twilight%20%E2%80%93%20T%E2%80%99%20Coffee%20House%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L123" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="54" customHeight="1">
       <x:c r="A124" s="4" t="str">
-        <x:v>Equilibrium Climbing Station</x:v>
+        <x:v>Vienna Bakehouse</x:v>
       </x:c>
       <x:c r="B124" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C124" s="4" t="str">
-        <x:v>Indiranagar</x:v>
+        <x:v>Koramangala</x:v>
       </x:c>
       <x:c r="D124" s="4" t="str">
-        <x:v>Indoor climbing option for a focused active session; confirm opening status and booking.</x:v>
+        <x:v>Bakery-cafe associated with coffee, baked goods and a slower service pace.</x:v>
       </x:c>
       <x:c r="E124" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Slow, cozy, pastry treat</x:v>
       </x:c>
       <x:c r="F124" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Calm atmosphere is noted by local listings; weekends may be busier.</x:v>
       </x:c>
       <x:c r="G124" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H124" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I124" s="4" t="str"/>
       <x:c r="J124" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K124" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Equilibrium%20Climbing%20Station%2C%20Indiranagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Vienna%20Bakehouse%2C%20Koramangala%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L124" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="54" customHeight="1">
       <x:c r="A125" s="4" t="str">
-        <x:v>Xtreme Zone</x:v>
+        <x:v>Conçu</x:v>
       </x:c>
       <x:c r="B125" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C125" s="4" t="str">
-        <x:v>Yelahanka / branch to confirm</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D125" s="4" t="str">
-        <x:v>Adventure activity operator candidate; verify current site and activity availability.</x:v>
+        <x:v>Patisserie and cafe for desserts, baked goods and a polished coffee break.</x:v>
       </x:c>
       <x:c r="E125" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Treat-yourself, elegant, unhurried</x:v>
       </x:c>
       <x:c r="F125" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Refined bakery-cafe ambience; likely busier at dessert and brunch peaks.</x:v>
       </x:c>
       <x:c r="G125" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹350–₹1,200</x:v>
       </x:c>
       <x:c r="H125" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I125" s="4" t="str"/>
       <x:c r="J125" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K125" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Xtreme%20Zone%2C%20Yelahanka%20%2F%20branch%20to%20confirm%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Con%C3%A7u%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L125" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="54" customHeight="1">
       <x:c r="A126" s="4" t="str">
-        <x:v>Flying Fox Adventure Park</x:v>
+        <x:v>The Leaf Table</x:v>
       </x:c>
       <x:c r="B126" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C126" s="4" t="str">
-        <x:v>Bannerghatta Road outskirts</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D126" s="4" t="str">
-        <x:v>Outdoor adventure experiences such as ropes and zipline-style activities; confirm operations.</x:v>
+        <x:v>Cafe and dining spot where ambience and service feature in local recommendations.</x:v>
       </x:c>
       <x:c r="E126" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Green, relaxed, catch-up</x:v>
       </x:c>
       <x:c r="F126" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Leafy or garden-leaning feel; confirm current seating and location.</x:v>
       </x:c>
       <x:c r="G126" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹300–₹1,000</x:v>
       </x:c>
       <x:c r="H126" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I126" s="4" t="str"/>
       <x:c r="J126" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K126" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Flying%20Fox%20Adventure%20Park%2C%20Bannerghatta%20Road%20outskirts%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Leaf%20Table%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L126" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="54" customHeight="1">
       <x:c r="A127" s="4" t="str">
-        <x:v>Area 83</x:v>
+        <x:v>Lick | Lavonne Ice Cream Kitchen</x:v>
       </x:c>
       <x:c r="B127" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C127" s="4" t="str">
-        <x:v>Ramanagara outskirts</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D127" s="4" t="str">
-        <x:v>Outdoor adventure resort with activity packages; travel time and bookings need planning.</x:v>
+        <x:v>Dessert and ice-cream cafe from the Lavonne family of food venues.</x:v>
       </x:c>
       <x:c r="E127" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Playful, sweet, treat stop</x:v>
       </x:c>
       <x:c r="F127" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Dessert-focused and social; not primarily a quiet work cafe.</x:v>
       </x:c>
       <x:c r="G127" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H127" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I127" s="4" t="str"/>
       <x:c r="J127" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K127" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Area%2083%2C%20Ramanagara%20outskirts%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lick%20%7C%20Lavonne%20Ice%20Cream%20Kitchen%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L127" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="54" customHeight="1">
       <x:c r="A128" s="4" t="str">
-        <x:v>Aruani Grid</x:v>
+        <x:v>Nomeli</x:v>
       </x:c>
       <x:c r="B128" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C128" s="4" t="str">
-        <x:v>Dommasandra</x:v>
+        <x:v>HAL 3rd Stage</x:v>
       </x:c>
       <x:c r="D128" s="4" t="str">
-        <x:v>Outdoor activity and adventure venue; confirm activity list and availability.</x:v>
+        <x:v>Small cafe listing with cookies as a signature draw.</x:v>
       </x:c>
       <x:c r="E128" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Cozy, sweet, neighbourhood</x:v>
       </x:c>
       <x:c r="F128" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Cookie-and-coffee stop; seating and current operation need confirmation.</x:v>
       </x:c>
       <x:c r="G128" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H128" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I128" s="4" t="str"/>
       <x:c r="J128" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K128" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Aruani%20Grid%2C%20Dommasandra%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Nomeli%2C%20HAL%203rd%20Stage%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L128" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="54" customHeight="1">
       <x:c r="A129" s="4" t="str">
-        <x:v>Go Kart Race Track, PLaY Arena</x:v>
+        <x:v>Mara</x:v>
       </x:c>
       <x:c r="B129" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C129" s="4" t="str">
-        <x:v>Kasavanahalli</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D129" s="4" t="str">
-        <x:v>Karting option within the PLaY Arena complex; separate activity charges may apply.</x:v>
+        <x:v>Cafe with coffee and refreshing drinks in HSR.</x:v>
       </x:c>
       <x:c r="E129" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Cute, easygoing, casual</x:v>
       </x:c>
       <x:c r="F129" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Local guide describes a cute cafe; expect atmosphere to vary by time.</x:v>
       </x:c>
       <x:c r="G129" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H129" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I129" s="4" t="str"/>
       <x:c r="J129" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K129" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Go%20Kart%20Race%20Track%2C%20PLaY%20Arena%2C%20Kasavanahalli%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Mara%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L129" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="54" customHeight="1">
       <x:c r="A130" s="4" t="str">
-        <x:v>Red Riders Gokarting</x:v>
+        <x:v>Eddy’s</x:v>
       </x:c>
       <x:c r="B130" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C130" s="4" t="str">
-        <x:v>Kodathi</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D130" s="4" t="str">
-        <x:v>Go-karting venue candidate on Bengaluru’s southeast edge; verify exact location and hours.</x:v>
+        <x:v>Breakfast cafe with coffee and all-day meal cues.</x:v>
       </x:c>
       <x:c r="E130" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Brunch, relaxed, catch-up</x:v>
       </x:c>
       <x:c r="F130" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Casual dining ambience; breakfast peak may be lively.</x:v>
       </x:c>
       <x:c r="G130" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹300–₹900</x:v>
       </x:c>
       <x:c r="H130" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I130" s="4" t="str"/>
       <x:c r="J130" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K130" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Red%20Riders%20Gokarting%2C%20Kodathi%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Eddy%E2%80%99s%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L130" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="54" customHeight="1">
       <x:c r="A131" s="4" t="str">
-        <x:v>Aladahalli Lake View GoKarting</x:v>
+        <x:v>Juno Coffee Club</x:v>
       </x:c>
       <x:c r="B131" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C131" s="4" t="str">
-        <x:v>Aladahalli outskirts</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D131" s="4" t="str">
-        <x:v>Go-karting listing with an outdoor setting; verify current operation before travelling.</x:v>
+        <x:v>Coffee-and-dessert stop with book, vinyl or manga-inspired interior cues.</x:v>
       </x:c>
       <x:c r="E131" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Cozy, playful, bookish</x:v>
       </x:c>
       <x:c r="F131" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Characterful decor; can be a lively cafe rather than silent study space.</x:v>
       </x:c>
       <x:c r="G131" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H131" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I131" s="4" t="str"/>
       <x:c r="J131" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K131" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Aladahalli%20Lake%20View%20GoKarting%2C%20Aladahalli%20outskirts%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Juno%20Coffee%20Club%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L131" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="54" customHeight="1">
       <x:c r="A132" s="4" t="str">
-        <x:v>Ramanagara rock climbing area</x:v>
+        <x:v>Terrabites</x:v>
       </x:c>
       <x:c r="B132" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C132" s="4" t="str">
-        <x:v>Ramanagara outskirts</x:v>
+        <x:v>Koramangala</x:v>
       </x:c>
       <x:c r="D132" s="4" t="str">
-        <x:v>Outdoor bouldering and climbing landscape; use a qualified guide and check access/weather.</x:v>
+        <x:v>Breakfast cafe described in local listings as peaceful and unhurried.</x:v>
       </x:c>
       <x:c r="E132" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Calm, slow breakfast, reset</x:v>
       </x:c>
       <x:c r="F132" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Quiet-breakfast cue is locally reported; verify current branch and timing.</x:v>
       </x:c>
       <x:c r="G132" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H132" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I132" s="4" t="str"/>
       <x:c r="J132" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K132" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ramanagara%20rock%20climbing%20area%2C%20Ramanagara%20outskirts%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Terrabites%2C%20Koramangala%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L132" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="54" customHeight="1">
       <x:c r="A133" s="4" t="str">
-        <x:v>Bowling at Phoenix Marketcity</x:v>
+        <x:v>Ground Up Coffee &amp; Roastery</x:v>
       </x:c>
       <x:c r="B133" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C133" s="4" t="str">
-        <x:v>Mahadevapura</x:v>
+        <x:v>Jayanagar</x:v>
       </x:c>
       <x:c r="D133" s="4" t="str">
-        <x:v>Mall-based bowling and arcade session; check operator, lanes and booking slots.</x:v>
+        <x:v>In-shop roastery for freshly roasted beans and coffee-focused visits.</x:v>
       </x:c>
       <x:c r="E133" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Coffee-minded, grounded, slow</x:v>
       </x:c>
       <x:c r="F133" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Roastery setting; ask about seating and quieter hours.</x:v>
       </x:c>
       <x:c r="G133" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹150–₹700</x:v>
       </x:c>
       <x:c r="H133" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I133" s="4" t="str"/>
       <x:c r="J133" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K133" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bowling%20at%20Phoenix%20Marketcity%2C%20Mahadevapura%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ground%20Up%20Coffee%20%26%20Roastery%2C%20Jayanagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L133" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="54" customHeight="1">
       <x:c r="A134" s="4" t="str">
-        <x:v>Laser tag at PLaY Arena</x:v>
+        <x:v>Roastea</x:v>
       </x:c>
       <x:c r="B134" s="4" t="str">
-        <x:v>Adventure &amp; Games</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C134" s="4" t="str">
-        <x:v>Kasavanahalli</x:v>
+        <x:v>Koramangala</x:v>
       </x:c>
       <x:c r="D134" s="4" t="str">
-        <x:v>Team laser-tag activity; venue rules and minimum group size may apply.</x:v>
+        <x:v>Cafe and tea/coffee stop for a casual meal or drink.</x:v>
       </x:c>
       <x:c r="E134" s="4" t="str">
-        <x:v>Playful, energetic, challenge-seeking</x:v>
+        <x:v>Easygoing, comfort, conversation</x:v>
       </x:c>
       <x:c r="F134" s="4" t="str">
-        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+        <x:v>Casual cafe ambience; current format and crowd vary.</x:v>
       </x:c>
       <x:c r="G134" s="4" t="str">
-        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H134" s="4" t="str">
-        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I134" s="4" t="str"/>
       <x:c r="J134" s="4" t="str">
-        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K134" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Laser%20tag%20at%20PLaY%20Arena%2C%20Kasavanahalli%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Roastea%2C%20Koramangala%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L134" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="54" customHeight="1">
       <x:c r="A135" s="4" t="str">
-        <x:v>Ranga Shankara</x:v>
+        <x:v>Brahma Cafe</x:v>
       </x:c>
       <x:c r="B135" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C135" s="4" t="str">
-        <x:v>JP Nagar</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D135" s="4" t="str">
-        <x:v>Respected theatre venue with a steady programme of Kannada and other-language plays.</x:v>
+        <x:v>Local tiffin-and-coffee cafe for thatte idli and filter coffee.</x:v>
       </x:c>
       <x:c r="E135" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Simple, comforting, local</x:v>
       </x:c>
       <x:c r="F135" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Quick, no-fuss breakfast stop; not a long-stay workspace.</x:v>
       </x:c>
       <x:c r="G135" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹50–₹350</x:v>
       </x:c>
       <x:c r="H135" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I135" s="4" t="str"/>
       <x:c r="J135" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K135" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ranga%20Shankara%2C%20JP%20Nagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Brahma%20Cafe%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L135" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="54" customHeight="1">
       <x:c r="A136" s="4" t="str">
-        <x:v>Chowdiah Memorial Hall</x:v>
+        <x:v>Paul Cafe</x:v>
       </x:c>
       <x:c r="B136" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C136" s="4" t="str">
-        <x:v>Vyalikaval</x:v>
+        <x:v>Orion Mall, Rajajinagar</x:v>
       </x:c>
       <x:c r="D136" s="4" t="str">
-        <x:v>Distinctive violin-shaped auditorium hosting music, dance and public events.</x:v>
+        <x:v>Bakery-cafe for croissants, desserts, coffee and a mall-side break.</x:v>
       </x:c>
       <x:c r="E136" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Treat, polished, people-watch</x:v>
       </x:c>
       <x:c r="F136" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Mall cafe with a terrace/view cue; busier during shopping hours.</x:v>
       </x:c>
       <x:c r="G136" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹350–₹1,200</x:v>
       </x:c>
       <x:c r="H136" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I136" s="4" t="str"/>
       <x:c r="J136" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K136" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Chowdiah%20Memorial%20Hall%2C%20Vyalikaval%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Paul%20Cafe%2C%20Orion%20Mall%2C%20Rajajinagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L136" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="54" customHeight="1">
       <x:c r="A137" s="4" t="str">
-        <x:v>Bangalore International Centre</x:v>
+        <x:v>The Fresh Factory</x:v>
       </x:c>
       <x:c r="B137" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C137" s="4" t="str">
-        <x:v>Domlur</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D137" s="4" t="str">
-        <x:v>Cultural centre for talks, performances, screenings and exhibitions.</x:v>
+        <x:v>Cafe and food market-style stop for breakfast, coffee and fresh items.</x:v>
       </x:c>
       <x:c r="E137" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Casual, bright, quick reset</x:v>
       </x:c>
       <x:c r="F137" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Informal cafe/grocery hybrid feel; verify seating availability.</x:v>
       </x:c>
       <x:c r="G137" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H137" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I137" s="4" t="str"/>
       <x:c r="J137" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K137" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bangalore%20International%20Centre%2C%20Domlur%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Fresh%20Factory%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L137" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="54" customHeight="1">
       <x:c r="A138" s="4" t="str">
-        <x:v>Lahe Lahe</x:v>
+        <x:v>Tan Coffee</x:v>
       </x:c>
       <x:c r="B138" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C138" s="4" t="str">
-        <x:v>Indiranagar</x:v>
+        <x:v>Koramangala</x:v>
       </x:c>
       <x:c r="D138" s="4" t="str">
-        <x:v>Community arts space for workshops, performances and creative gatherings.</x:v>
+        <x:v>Coffee-first cafe recently surfaced in local Bengaluru recommendations.</x:v>
       </x:c>
       <x:c r="E138" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Focused, contemporary, coffee-led</x:v>
       </x:c>
       <x:c r="F138" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Bright, modern coffee-bar cue; quietness not assured.</x:v>
       </x:c>
       <x:c r="G138" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H138" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I138" s="4" t="str"/>
       <x:c r="J138" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K138" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lahe%20Lahe%2C%20Indiranagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Tan%20Coffee%2C%20Koramangala%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L138" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="54" customHeight="1">
       <x:c r="A139" s="4" t="str">
-        <x:v>Jagriti Theatre</x:v>
+        <x:v>Ela Matcha</x:v>
       </x:c>
       <x:c r="B139" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C139" s="4" t="str">
-        <x:v>Whitefield</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D139" s="4" t="str">
-        <x:v>Theatre venue with plays and cultural programming; check schedule.</x:v>
+        <x:v>Matcha and cafe drinks for a lighter, tea-forward stop.</x:v>
       </x:c>
       <x:c r="E139" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Gentle, curious, refreshing</x:v>
       </x:c>
       <x:c r="F139" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Small beverage-led cafe; seating and hours should be checked.</x:v>
       </x:c>
       <x:c r="G139" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H139" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I139" s="4" t="str"/>
       <x:c r="J139" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K139" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jagriti%20Theatre%2C%20Whitefield%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ela%20Matcha%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L139" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="54" customHeight="1">
       <x:c r="A140" s="4" t="str">
-        <x:v>Alliance Française de Bangalore</x:v>
+        <x:v>Molly’s Courtyard</x:v>
       </x:c>
       <x:c r="B140" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C140" s="4" t="str">
-        <x:v>Vasanth Nagar</x:v>
+        <x:v>Cunningham Road</x:v>
       </x:c>
       <x:c r="D140" s="4" t="str">
-        <x:v>French cultural centre with film, art, language and performance events.</x:v>
+        <x:v>Courtyard cafe where the setting is part of the visit.</x:v>
       </x:c>
       <x:c r="E140" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Cozy, leafy, date or solo pause</x:v>
       </x:c>
       <x:c r="F140" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Courtyard atmosphere is the draw; confirm access and current operation.</x:v>
       </x:c>
       <x:c r="G140" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹300–₹1,000</x:v>
       </x:c>
       <x:c r="H140" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I140" s="4" t="str"/>
       <x:c r="J140" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K140" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Alliance%20Fran%C3%A7aise%20de%20Bangalore%2C%20Vasanth%20Nagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Molly%E2%80%99s%20Courtyard%2C%20Cunningham%20Road%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L140" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="54" customHeight="1">
       <x:c r="A141" s="4" t="str">
-        <x:v>Goethe-Institut / Max Mueller Bhavan</x:v>
+        <x:v>1966 Mumbai Cafe</x:v>
       </x:c>
       <x:c r="B141" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C141" s="4" t="str">
         <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D141" s="4" t="str">
-        <x:v>German cultural institute with talks, screenings, exhibitions and performances.</x:v>
+        <x:v>Cafe serving Mumbai-style snacks such as vada pav and misal pav.</x:v>
       </x:c>
       <x:c r="E141" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Nostalgic, snacky, casual</x:v>
       </x:c>
       <x:c r="F141" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Casual snack-cafe; likely lively around meal times.</x:v>
       </x:c>
       <x:c r="G141" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹100–₹500</x:v>
       </x:c>
       <x:c r="H141" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I141" s="4" t="str"/>
       <x:c r="J141" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K141" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Goethe-Institut%20%2F%20Max%20Mueller%20Bhavan%2C%20Indiranagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=1966%20Mumbai%20Cafe%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L141" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="54" customHeight="1">
       <x:c r="A142" s="4" t="str">
-        <x:v>Bangalore Gayana Samaja</x:v>
+        <x:v>ChayaChyll Cafe</x:v>
       </x:c>
       <x:c r="B142" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C142" s="4" t="str">
-        <x:v>Basavanagudi</x:v>
+        <x:v>Whitefield</x:v>
       </x:c>
       <x:c r="D142" s="4" t="str">
-        <x:v>Long-running venue for classical music, dance and cultural performances.</x:v>
+        <x:v>Cafe with tea, matcha, brunch and dessert options in Whitefield.</x:v>
       </x:c>
       <x:c r="E142" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Comfort, sweet break, catch-up</x:v>
       </x:c>
       <x:c r="F142" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Contemporary cafe setting; current noise and seating vary.</x:v>
       </x:c>
       <x:c r="G142" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹250–₹850</x:v>
       </x:c>
       <x:c r="H142" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I142" s="4" t="str"/>
       <x:c r="J142" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K142" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bangalore%20Gayana%20Samaja%2C%20Basavanagudi%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=ChayaChyll%20Cafe%2C%20Whitefield%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L142" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="54" customHeight="1">
       <x:c r="A143" s="4" t="str">
-        <x:v>Karnataka Chitrakala Parishath galleries</x:v>
+        <x:v>Cafe Komorebi</x:v>
       </x:c>
       <x:c r="B143" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C143" s="4" t="str">
-        <x:v>Kumara Krupa Road</x:v>
+        <x:v>Sarjapur</x:v>
       </x:c>
       <x:c r="D143" s="4" t="str">
-        <x:v>Gallery campus for exhibitions, folk art and visual-culture events.</x:v>
+        <x:v>Farm-side cafe described as a slow meal among trees with a changing menu.</x:v>
       </x:c>
       <x:c r="E143" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Slow, nature-rich, escape</x:v>
       </x:c>
       <x:c r="F143" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Tree-filled farm setting; verify exact location, access and opening schedule.</x:v>
       </x:c>
       <x:c r="G143" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹350–₹1,200</x:v>
       </x:c>
       <x:c r="H143" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I143" s="4" t="str"/>
       <x:c r="J143" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K143" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Karnataka%20Chitrakala%20Parishath%20galleries%2C%20Kumara%20Krupa%20Road%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Komorebi%2C%20Sarjapur%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L143" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="54" customHeight="1">
       <x:c r="A144" s="4" t="str">
-        <x:v>Museum of Art &amp; Photography events</x:v>
+        <x:v>Beans of Bodhi</x:v>
       </x:c>
       <x:c r="B144" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C144" s="4" t="str">
-        <x:v>Cubbon Road</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D144" s="4" t="str">
-        <x:v>Talks, workshops and exhibitions within a contemporary art museum.</x:v>
+        <x:v>Coffee and cafe stop with distinctive, architectural interior styling.</x:v>
       </x:c>
       <x:c r="E144" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Design-minded, curious, coffee</x:v>
       </x:c>
       <x:c r="F144" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Minimal/brutalist design cue; check current seating for longer stays.</x:v>
       </x:c>
       <x:c r="G144" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H144" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I144" s="4" t="str"/>
       <x:c r="J144" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K144" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Museum%20of%20Art%20%26%20Photography%20events%2C%20Cubbon%20Road%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Beans%20of%20Bodhi%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L144" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="54" customHeight="1">
       <x:c r="A145" s="4" t="str">
-        <x:v>National Gallery of Modern Art events</x:v>
+        <x:v>The Coffee San</x:v>
       </x:c>
       <x:c r="B145" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C145" s="4" t="str">
-        <x:v>Vasanth Nagar</x:v>
+        <x:v>V.V. Puram</x:v>
       </x:c>
       <x:c r="D145" s="4" t="str">
-        <x:v>Exhibitions and cultural programmes in a heritage gallery setting.</x:v>
+        <x:v>Coffee place with patio seating in the V.V. Puram area.</x:v>
       </x:c>
       <x:c r="E145" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Open-air, mellow, local</x:v>
       </x:c>
       <x:c r="F145" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Patio seating is noted; visit outside food-street peak times for a calmer pause.</x:v>
       </x:c>
       <x:c r="G145" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹150–₹600</x:v>
       </x:c>
       <x:c r="H145" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I145" s="4" t="str"/>
       <x:c r="J145" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K145" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=National%20Gallery%20of%20Modern%20Art%20events%2C%20Vasanth%20Nagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Coffee%20San%2C%20V.V.%20Puram%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L145" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="54" customHeight="1">
       <x:c r="A146" s="4" t="str">
-        <x:v>Bangalore Creative Circus</x:v>
+        <x:v>Shinto</x:v>
       </x:c>
       <x:c r="B146" s="4" t="str">
-        <x:v>Arts &amp; Performance</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C146" s="4" t="str">
-        <x:v>Yeshwanthpur</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D146" s="4" t="str">
-        <x:v>Creative and sustainability-focused community campus; public programmes vary.</x:v>
+        <x:v>Quaint cafe-style coffee stop known for cold brews.</x:v>
       </x:c>
       <x:c r="E146" s="4" t="str">
-        <x:v>Inspired, expressive, immersed</x:v>
+        <x:v>Quiet coffee, small treat, mellow</x:v>
       </x:c>
       <x:c r="F146" s="4" t="str">
-        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+        <x:v>Quaint setting is reported; verify current address and seating.</x:v>
       </x:c>
       <x:c r="G146" s="4" t="str">
-        <x:v>Free–₹2,000+ depending on event</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H146" s="4" t="str">
-        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I146" s="4" t="str"/>
       <x:c r="J146" s="4" t="str">
-        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K146" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bangalore%20Creative%20Circus%2C%20Yeshwanthpur%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Shinto%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L146" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="54" customHeight="1">
       <x:c r="A147" s="4" t="str">
-        <x:v>KR Market (City Market)</x:v>
+        <x:v>Diha Cafe</x:v>
       </x:c>
       <x:c r="B147" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C147" s="4" t="str">
-        <x:v>Kalassipalya</x:v>
+        <x:v>JP Nagar</x:v>
       </x:c>
       <x:c r="D147" s="4" t="str">
-        <x:v>Dense wholesale market known for flowers, produce and early-morning city rhythms.</x:v>
+        <x:v>Neighbourhood cafe for coffee, cold coffee and casual food.</x:v>
       </x:c>
       <x:c r="E147" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Simple, friendly, low-key</x:v>
       </x:c>
       <x:c r="F147" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Local cafe setting; quieter periods should be checked on arrival.</x:v>
       </x:c>
       <x:c r="G147" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H147" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I147" s="4" t="str"/>
       <x:c r="J147" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K147" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=KR%20Market%20(City%20Market)%2C%20Kalassipalya%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Diha%20Cafe%2C%20JP%20Nagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L147" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="54" customHeight="1">
       <x:c r="A148" s="4" t="str">
-        <x:v>Commercial Street</x:v>
+        <x:v>The Craftery by Subko</x:v>
       </x:c>
       <x:c r="B148" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C148" s="4" t="str">
-        <x:v>Tasker Town</x:v>
+        <x:v>Koramangala</x:v>
       </x:c>
       <x:c r="D148" s="4" t="str">
-        <x:v>Busy shopping district for clothes, shoes, accessories and street food.</x:v>
+        <x:v>Bakery and cafe from Subko with coffee, breads and brunch-style plates.</x:v>
       </x:c>
       <x:c r="E148" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Craft, slow brunch, sensory</x:v>
       </x:c>
       <x:c r="F148" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Craft bakery atmosphere; likely busier during brunch.</x:v>
       </x:c>
       <x:c r="G148" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹350–₹1,200</x:v>
       </x:c>
       <x:c r="H148" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I148" s="4" t="str"/>
       <x:c r="J148" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K148" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Commercial%20Street%2C%20Tasker%20Town%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Craftery%20by%20Subko%2C%20Koramangala%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L148" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="54" customHeight="1">
       <x:c r="A149" s="4" t="str">
-        <x:v>Church Street</x:v>
+        <x:v>Kahale</x:v>
       </x:c>
       <x:c r="B149" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C149" s="4" t="str">
-        <x:v>Central Business District</x:v>
+        <x:v>Jayanagar</x:v>
       </x:c>
       <x:c r="D149" s="4" t="str">
-        <x:v>Walkable high street with bookstores, cafes and retail.</x:v>
+        <x:v>Coffee concept space with filter coffee and local cafe character.</x:v>
       </x:c>
       <x:c r="E149" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Local, thoughtful, coffee-first</x:v>
       </x:c>
       <x:c r="F149" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Concept-store/cafe feel; check whether seating is suited to a long visit.</x:v>
       </x:c>
       <x:c r="G149" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹100–₹500</x:v>
       </x:c>
       <x:c r="H149" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I149" s="4" t="str"/>
       <x:c r="J149" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K149" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Church%20Street%2C%20Central%20Business%20District%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kahale%2C%20Jayanagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L149" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="54" customHeight="1">
       <x:c r="A150" s="4" t="str">
-        <x:v>MG Road</x:v>
+        <x:v>Sakura Matcha Bar</x:v>
       </x:c>
       <x:c r="B150" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C150" s="4" t="str">
-        <x:v>Central Business District</x:v>
+        <x:v>Victoria Layout</x:v>
       </x:c>
       <x:c r="D150" s="4" t="str">
-        <x:v>Central shopping and transit corridor with retail, dining and city landmarks.</x:v>
+        <x:v>Matcha-focused bar serving drinks and small Japanese-inspired bites.</x:v>
       </x:c>
       <x:c r="E150" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Gentle, curious, cozy</x:v>
       </x:c>
       <x:c r="F150" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Small matcha-bar vibe; seating may be limited.</x:v>
       </x:c>
       <x:c r="G150" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H150" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I150" s="4" t="str"/>
       <x:c r="J150" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K150" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=MG%20Road%2C%20Central%20Business%20District%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sakura%20Matcha%20Bar%2C%20Victoria%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L150" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="54" customHeight="1">
       <x:c r="A151" s="4" t="str">
-        <x:v>Brigade Road</x:v>
+        <x:v>Turtle Matcha Bar</x:v>
       </x:c>
       <x:c r="B151" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C151" s="4" t="str">
-        <x:v>Central Business District</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D151" s="4" t="str">
-        <x:v>Lively retail and dining street linking MG Road and Residency Road.</x:v>
+        <x:v>Matcha and specialty drinks with seasonal flavour combinations.</x:v>
       </x:c>
       <x:c r="E151" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Fresh, playful, slow sip</x:v>
       </x:c>
       <x:c r="F151" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Beverage-led cafe; current seating and busy times vary.</x:v>
       </x:c>
       <x:c r="G151" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H151" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I151" s="4" t="str"/>
       <x:c r="J151" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K151" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Brigade%20Road%2C%20Central%20Business%20District%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Turtle%20Matcha%20Bar%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L151" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="54" customHeight="1">
       <x:c r="A152" s="4" t="str">
-        <x:v>Jayanagar 4th Block Shopping Complex</x:v>
+        <x:v>Kink Coffee</x:v>
       </x:c>
       <x:c r="B152" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C152" s="4" t="str">
-        <x:v>Jayanagar</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D152" s="4" t="str">
-        <x:v>Neighbourhood shopping hub with street stalls, stores and quick eats.</x:v>
+        <x:v>Coffee and pastry stop with flavoured latte and bakery options.</x:v>
       </x:c>
       <x:c r="E152" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Sweet, cozy, coffee break</x:v>
       </x:c>
       <x:c r="F152" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Small cafe-style setting; verify current operating details.</x:v>
       </x:c>
       <x:c r="G152" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H152" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I152" s="4" t="str"/>
       <x:c r="J152" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K152" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jayanagar%204th%20Block%20Shopping%20Complex%2C%20Jayanagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kink%20Coffee%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L152" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="54" customHeight="1">
       <x:c r="A153" s="4" t="str">
-        <x:v>Gandhi Bazaar</x:v>
+        <x:v>The Chaitini</x:v>
       </x:c>
       <x:c r="B153" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C153" s="4" t="str">
-        <x:v>Basavanagudi</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D153" s="4" t="str">
-        <x:v>Traditional market street for flowers, produce, sweets and local shopping.</x:v>
+        <x:v>Tea-and-snack shop with iced filter coffee, cake and bun maska.</x:v>
       </x:c>
       <x:c r="E153" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Lively, nostalgic, quick comfort</x:v>
       </x:c>
       <x:c r="F153" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Small and often crowded per local guide; not ideal for quiet work.</x:v>
       </x:c>
       <x:c r="G153" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹80–₹400</x:v>
       </x:c>
       <x:c r="H153" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I153" s="4" t="str"/>
       <x:c r="J153" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K153" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gandhi%20Bazaar%2C%20Basavanagudi%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Chaitini%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L153" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="54" customHeight="1">
       <x:c r="A154" s="4" t="str">
-        <x:v>Chickpet Market</x:v>
+        <x:v>Beku</x:v>
       </x:c>
       <x:c r="B154" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C154" s="4" t="str">
-        <x:v>Chickpet</x:v>
+        <x:v>JP Nagar</x:v>
       </x:c>
       <x:c r="D154" s="4" t="str">
-        <x:v>Wholesale textile and trading district; busy lanes reward unhurried browsing.</x:v>
+        <x:v>Bookshop-cafe for reading, coffee and a slower solo visit.</x:v>
       </x:c>
       <x:c r="E154" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Quiet, bookish, cozy</x:v>
       </x:c>
       <x:c r="F154" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Reading-oriented bookshop-cafe; confirm seating and laptop policy.</x:v>
       </x:c>
       <x:c r="G154" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H154" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I154" s="4" t="str"/>
       <x:c r="J154" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K154" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Chickpet%20Market%2C%20Chickpet%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Beku%2C%20JP%20Nagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L154" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="54" customHeight="1">
       <x:c r="A155" s="4" t="str">
-        <x:v>Avenue Road</x:v>
+        <x:v>Karadi Coffee</x:v>
       </x:c>
       <x:c r="B155" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C155" s="4" t="str">
-        <x:v>Central Bengaluru</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D155" s="4" t="str">
-        <x:v>Bookshops, stationery, paper and old-city trading streets.</x:v>
+        <x:v>Coffee shop with baked treats and a work-friendly feel in local listings.</x:v>
       </x:c>
       <x:c r="E155" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Focused, cozy, low-key</x:v>
       </x:c>
       <x:c r="F155" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Comfortable work cue is reported; check Wi-Fi, sockets and weekend policy.</x:v>
       </x:c>
       <x:c r="G155" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H155" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I155" s="4" t="str"/>
       <x:c r="J155" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K155" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Avenue%20Road%2C%20Central%20Bengaluru%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Karadi%20Coffee%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L155" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="54" customHeight="1">
       <x:c r="A156" s="4" t="str">
-        <x:v>Russell Market</x:v>
+        <x:v>Nombre Specialty Coffee</x:v>
       </x:c>
       <x:c r="B156" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C156" s="4" t="str">
-        <x:v>Shivajinagar</x:v>
+        <x:v>JP Nagar</x:v>
       </x:c>
       <x:c r="D156" s="4" t="str">
-        <x:v>Historic indoor market for produce, meat, flowers and everyday goods.</x:v>
+        <x:v>Specialty coffee cafe described as especially quiet in the mornings.</x:v>
       </x:c>
       <x:c r="E156" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Calm, focused, coffee ritual</x:v>
       </x:c>
       <x:c r="F156" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Quiet-morning cue; seating, power and laptop rules need direct confirmation.</x:v>
       </x:c>
       <x:c r="G156" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹200–₹800</x:v>
       </x:c>
       <x:c r="H156" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I156" s="4" t="str"/>
       <x:c r="J156" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K156" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Russell%20Market%2C%20Shivajinagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Nombre%20Specialty%20Coffee%2C%20JP%20Nagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L156" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="54" customHeight="1">
       <x:c r="A157" s="4" t="str">
-        <x:v>UB City</x:v>
+        <x:v>Ink &amp; Oak</x:v>
       </x:c>
       <x:c r="B157" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C157" s="4" t="str">
-        <x:v>Vittal Mallya Road</x:v>
+        <x:v>HSR Layout</x:v>
       </x:c>
       <x:c r="D157" s="4" t="str">
-        <x:v>Upscale retail and dining complex with an open-air courtyard.</x:v>
+        <x:v>Bookshop-cafe combining coffee with browsing and reading.</x:v>
       </x:c>
       <x:c r="E157" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Bookish, cozy, reflective</x:v>
       </x:c>
       <x:c r="F157" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Bookstore-cafe ambience; check whether long stays are welcome.</x:v>
       </x:c>
       <x:c r="G157" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹250–₹800</x:v>
       </x:c>
       <x:c r="H157" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I157" s="4" t="str"/>
       <x:c r="J157" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K157" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=UB%20City%2C%20Vittal%20Mallya%20Road%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ink%20%26%20Oak%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L157" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="54" customHeight="1">
       <x:c r="A158" s="4" t="str">
-        <x:v>Orion Mall</x:v>
+        <x:v>Still Coffee</x:v>
       </x:c>
       <x:c r="B158" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C158" s="4" t="str">
-        <x:v>Rajajinagar</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D158" s="4" t="str">
-        <x:v>Large mall with shopping, dining and entertainment by a lakefront promenade.</x:v>
+        <x:v>Small specialty coffee counter in a home-style setting.</x:v>
       </x:c>
       <x:c r="E158" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Minimal, coffee-focused, slow</x:v>
       </x:c>
       <x:c r="F158" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Intimate kerbside/home setting; seating may be limited.</x:v>
       </x:c>
       <x:c r="G158" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹150–₹600</x:v>
       </x:c>
       <x:c r="H158" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I158" s="4" t="str"/>
       <x:c r="J158" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K158" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Orion%20Mall%2C%20Rajajinagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Still%20Coffee%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L158" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="54" customHeight="1">
       <x:c r="A159" s="4" t="str">
-        <x:v>Phoenix Marketcity</x:v>
+        <x:v>Beanlore Coffee Roasters</x:v>
       </x:c>
       <x:c r="B159" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C159" s="4" t="str">
-        <x:v>Mahadevapura</x:v>
+        <x:v>HSR Layout / verify branch</x:v>
       </x:c>
       <x:c r="D159" s="4" t="str">
-        <x:v>Large retail and entertainment mall on the eastern side of the city.</x:v>
+        <x:v>Specialty roastery-cafe listed for coffee, calm weekdays and work sessions.</x:v>
       </x:c>
       <x:c r="E159" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Focused, cozy, coffee craft</x:v>
       </x:c>
       <x:c r="F159" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Natural-light, laptop-friendly cues in guide; verify exact branch and weekend policy.</x:v>
       </x:c>
       <x:c r="G159" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹250–₹900</x:v>
       </x:c>
       <x:c r="H159" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I159" s="4" t="str"/>
       <x:c r="J159" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K159" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Phoenix%20Marketcity%2C%20Mahadevapura%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Beanlore%20Coffee%20Roasters%2C%20HSR%20Layout%20%2F%20verify%20branch%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L159" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="54" customHeight="1">
       <x:c r="A160" s="4" t="str">
-        <x:v>Mantri Square Mall</x:v>
+        <x:v>Bengaluru Cafe</x:v>
       </x:c>
       <x:c r="B160" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C160" s="4" t="str">
         <x:v>Malleshwaram</x:v>
       </x:c>
       <x:c r="D160" s="4" t="str">
-        <x:v>Transit-connected shopping and entertainment mall.</x:v>
+        <x:v>Cafe with a designed interior and a broad casual menu.</x:v>
       </x:c>
       <x:c r="E160" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Easygoing, local, catch-up</x:v>
       </x:c>
       <x:c r="F160" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Neighbourhood cafe; check current crowd before planning quiet work.</x:v>
       </x:c>
       <x:c r="G160" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H160" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I160" s="4" t="str"/>
       <x:c r="J160" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K160" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Mantri%20Square%20Mall%2C%20Malleshwaram%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bengaluru%20Cafe%2C%20Malleshwaram%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L160" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="54" customHeight="1">
       <x:c r="A161" s="4" t="str">
-        <x:v>Lulu Mall Bengaluru</x:v>
+        <x:v>Drip Drop</x:v>
       </x:c>
       <x:c r="B161" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C161" s="4" t="str">
-        <x:v>Gopalapura / Mysore Road</x:v>
+        <x:v>JP Nagar</x:v>
       </x:c>
       <x:c r="D161" s="4" t="str">
-        <x:v>Large mall with retail, food and family entertainment; check current events.</x:v>
+        <x:v>Coffee-bar cafe with a bright, compact interior.</x:v>
       </x:c>
       <x:c r="E161" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Bright, quick reset, coffee-first</x:v>
       </x:c>
       <x:c r="F161" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Coffee-bar style; likely better for a short stop than a long work session.</x:v>
       </x:c>
       <x:c r="G161" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹150–₹650</x:v>
       </x:c>
       <x:c r="H161" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I161" s="4" t="str"/>
       <x:c r="J161" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K161" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lulu%20Mall%20Bengaluru%2C%20Gopalapura%20%2F%20Mysore%20Road%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Drip%20Drop%2C%20JP%20Nagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L161" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="54" customHeight="1">
       <x:c r="A162" s="4" t="str">
-        <x:v>Brigade Orion East</x:v>
+        <x:v>Old Bangalore</x:v>
       </x:c>
       <x:c r="B162" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C162" s="4" t="str">
-        <x:v>Banaswadi</x:v>
+        <x:v>Banashankari</x:v>
       </x:c>
       <x:c r="D162" s="4" t="str">
-        <x:v>Neighbourhood mall and dining hub in northeast Bengaluru.</x:v>
+        <x:v>Cafe/food stop for traditional Karnataka dishes and local breakfast flavours.</x:v>
       </x:c>
       <x:c r="E162" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Nostalgic, comforting, local</x:v>
       </x:c>
       <x:c r="F162" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Traditional food-led cafe; busier at breakfast and lunch.</x:v>
       </x:c>
       <x:c r="G162" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹100–₹500</x:v>
       </x:c>
       <x:c r="H162" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I162" s="4" t="str"/>
       <x:c r="J162" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K162" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Brigade%20Orion%20East%2C%20Banaswadi%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Old%20Bangalore%2C%20Banashankari%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L162" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="54" customHeight="1">
       <x:c r="A163" s="4" t="str">
-        <x:v>Sankey Road design and retail stretch</x:v>
+        <x:v>The Filter Coffee</x:v>
       </x:c>
       <x:c r="B163" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C163" s="4" t="str">
-        <x:v>Vasanth Nagar</x:v>
+        <x:v>Indiranagar</x:v>
       </x:c>
       <x:c r="D163" s="4" t="str">
-        <x:v>Small boutiques and cafes in a leafy central neighbourhood.</x:v>
+        <x:v>Breakfast and filter-coffee cafe with South Indian tiffin options.</x:v>
       </x:c>
       <x:c r="E163" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Simple, comforting, familiar</x:v>
       </x:c>
       <x:c r="F163" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Quick tiffin format; good for a short coffee stop, not a quiet work session.</x:v>
       </x:c>
       <x:c r="G163" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹50–₹350</x:v>
       </x:c>
       <x:c r="H163" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I163" s="4" t="str"/>
       <x:c r="J163" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K163" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sankey%20Road%20design%20and%20retail%20stretch%2C%20Vasanth%20Nagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Filter%20Coffee%2C%20Indiranagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L163" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="54" customHeight="1">
       <x:c r="A164" s="4" t="str">
-        <x:v>National Market</x:v>
+        <x:v>Cafe Amudham</x:v>
       </x:c>
       <x:c r="B164" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C164" s="4" t="str">
-        <x:v>Gandhinagar</x:v>
+        <x:v>Koramangala</x:v>
       </x:c>
       <x:c r="D164" s="4" t="str">
-        <x:v>Compact electronics and retail market; compare prices and check item warranties.</x:v>
+        <x:v>South Indian tiffin cafe known for idli varieties and strong filter coffee.</x:v>
       </x:c>
       <x:c r="E164" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Comforting, local, budget-friendly</x:v>
       </x:c>
       <x:c r="F164" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Casual tiffin-cafe ambience; expect meal-time bustle.</x:v>
       </x:c>
       <x:c r="G164" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹50–₹350</x:v>
       </x:c>
       <x:c r="H164" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I164" s="4" t="str"/>
       <x:c r="J164" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://cafeblr.com/</x:v>
       </x:c>
       <x:c r="K164" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=National%20Market%2C%20Gandhinagar%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Amudham%2C%20Koramangala%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L164" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="54" customHeight="1">
       <x:c r="A165" s="4" t="str">
-        <x:v>Malleswaram 8th Cross Market</x:v>
+        <x:v>Ajji House by Subko</x:v>
       </x:c>
       <x:c r="B165" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C165" s="4" t="str">
-        <x:v>Malleshwaram</x:v>
+        <x:v>Shanti Nagar</x:v>
       </x:c>
       <x:c r="D165" s="4" t="str">
-        <x:v>Traditional neighbourhood shopping lane with produce, flowers and snacks.</x:v>
+        <x:v>Cafe in a restored home with a shaded courtyard and heritage-home character.</x:v>
       </x:c>
       <x:c r="E165" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Cozy, reflective, slow coffee</x:v>
       </x:c>
       <x:c r="F165" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Restored-home setting and tree-shaded courtyard; check table availability.</x:v>
       </x:c>
       <x:c r="G165" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹350–₹1,200</x:v>
       </x:c>
       <x:c r="H165" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I165" s="4" t="str"/>
       <x:c r="J165" s="4" t="str">
-        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
       </x:c>
       <x:c r="K165" s="4" t="str">
-        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Malleswaram%208th%20Cross%20Market%2C%20Malleshwaram%2C%20Bengaluru</x:v>
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ajji%20House%20by%20Subko%2C%20Shanti%20Nagar%2C%20Bengaluru</x:v>
       </x:c>
       <x:c r="L165" s="4" t="str">
-        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="54" customHeight="1">
       <x:c r="A166" s="4" t="str">
-        <x:v>V.V. Puram Thindi Beedi</x:v>
+        <x:v>The Ants Cafe</x:v>
       </x:c>
       <x:c r="B166" s="4" t="str">
-        <x:v>Markets &amp; Shopping</x:v>
+        <x:v>Cafés &amp; Bakeries</x:v>
       </x:c>
       <x:c r="C166" s="4" t="str">
-        <x:v>V.V. Puram</x:v>
+        <x:v>Whitefield</x:v>
       </x:c>
       <x:c r="D166" s="4" t="str">
-        <x:v>Food-focused street market and evening snack crawl.</x:v>
+        <x:v>Garden cafe associated with greenery, a craft store and relaxed longer visits.</x:v>
       </x:c>
       <x:c r="E166" s="4" t="str">
-        <x:v>Browse, discover, people-watch</x:v>
+        <x:v>Leafy calm, reading, longer visit</x:v>
       </x:c>
       <x:c r="F166" s="4" t="str">
-        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+        <x:v>Garden cafe with a craft-store context; weekday visits are more likely to feel unhurried.</x:v>
       </x:c>
       <x:c r="G166" s="4" t="str">
-        <x:v>No entry fee; shopping spend varies widely</x:v>
+        <x:v>₹200–₹700</x:v>
       </x:c>
       <x:c r="H166" s="4" t="str">
-        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
       </x:c>
       <x:c r="I166" s="4" t="str"/>
       <x:c r="J166" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K166" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Ants%20Cafe%2C%20Whitefield%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L166" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="54" customHeight="1">
+      <x:c r="A167" s="4" t="str">
+        <x:v>The Caffeine Baar</x:v>
+      </x:c>
+      <x:c r="B167" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C167" s="4" t="str">
+        <x:v>Jayanagar / JP Nagar</x:v>
+      </x:c>
+      <x:c r="D167" s="4" t="str">
+        <x:v>Coffee roastery cafe with natural light, Wi-Fi and power points reported in city guide.</x:v>
+      </x:c>
+      <x:c r="E167" s="4" t="str">
+        <x:v>Focused work, specialty coffee</x:v>
+      </x:c>
+      <x:c r="F167" s="4" t="str">
+        <x:v>Guide reports natural light, Wi-Fi and sockets; confirm exact branch and current amenities.</x:v>
+      </x:c>
+      <x:c r="G167" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H167" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I167" s="4" t="str"/>
+      <x:c r="J167" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K167" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Caffeine%20Baar%2C%20Jayanagar%20%2F%20JP%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L167" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="54" customHeight="1">
+      <x:c r="A168" s="4" t="str">
+        <x:v>The Kind Roastery &amp; Brew Room</x:v>
+      </x:c>
+      <x:c r="B168" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C168" s="4" t="str">
+        <x:v>Indiranagar / JP Nagar; branch verify</x:v>
+      </x:c>
+      <x:c r="D168" s="4" t="str">
+        <x:v>Vegetarian specialty coffee cafe with natural light and power points.</x:v>
+      </x:c>
+      <x:c r="E168" s="4" t="str">
+        <x:v>Quiet weekday, plant-based, coffee-focused</x:v>
+      </x:c>
+      <x:c r="F168" s="4" t="str">
+        <x:v>Laptop-friendly on weekdays; guide reports a weekend laptop restriction at the JP Nagar venue.</x:v>
+      </x:c>
+      <x:c r="G168" s="4" t="str">
+        <x:v>₹250–₹900</x:v>
+      </x:c>
+      <x:c r="H168" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I168" s="4" t="str"/>
+      <x:c r="J168" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K168" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Kind%20Roastery%20%26%20Brew%20Room%2C%20Indiranagar%20%2F%20JP%20Nagar%3B%20branch%20verify%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L168" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="54" customHeight="1">
+      <x:c r="A169" s="4" t="str">
+        <x:v>The Roastery Coffee House</x:v>
+      </x:c>
+      <x:c r="B169" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C169" s="4" t="str">
+        <x:v>Kalyan Nagar</x:v>
+      </x:c>
+      <x:c r="D169" s="4" t="str">
+        <x:v>Coffee roastery and cafe for fresh-roast aromas and a longer coffee visit.</x:v>
+      </x:c>
+      <x:c r="E169" s="4" t="str">
+        <x:v>Coffee-minded, cozy, exploratory</x:v>
+      </x:c>
+      <x:c r="F169" s="4" t="str">
+        <x:v>Roastery ambience; guide notes weekend/evening crowding, so weekdays are calmer.</x:v>
+      </x:c>
+      <x:c r="G169" s="4" t="str">
+        <x:v>₹250–₹900</x:v>
+      </x:c>
+      <x:c r="H169" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I169" s="4" t="str"/>
+      <x:c r="J169" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K169" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Roastery%20Coffee%20House%2C%20Kalyan%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L169" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="54" customHeight="1">
+      <x:c r="A170" s="4" t="str">
+        <x:v>Copper + Cloves</x:v>
+      </x:c>
+      <x:c r="B170" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C170" s="4" t="str">
+        <x:v>Bengaluru (branch verify)</x:v>
+      </x:c>
+      <x:c r="D170" s="4" t="str">
+        <x:v>Plant-filled cafe with a bookshop component and vegetarian menu.</x:v>
+      </x:c>
+      <x:c r="E170" s="4" t="str">
+        <x:v>Calm, leafy, bookish</x:v>
+      </x:c>
+      <x:c r="F170" s="4" t="str">
+        <x:v>Plants and bookshop are noted; confirm exact branch and current vibe.</x:v>
+      </x:c>
+      <x:c r="G170" s="4" t="str">
+        <x:v>₹300–₹1,000</x:v>
+      </x:c>
+      <x:c r="H170" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I170" s="4" t="str"/>
+      <x:c r="J170" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K170" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Copper%20%2B%20Cloves%2C%20Bengaluru%20(branch%20verify)%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L170" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="54" customHeight="1">
+      <x:c r="A171" s="4" t="str">
+        <x:v>Yogisthaan</x:v>
+      </x:c>
+      <x:c r="B171" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C171" s="4" t="str">
+        <x:v>Indiranagar</x:v>
+      </x:c>
+      <x:c r="D171" s="4" t="str">
+        <x:v>Plant-forward cafe with a quiet-oriented policy and covered outdoor seating.</x:v>
+      </x:c>
+      <x:c r="E171" s="4" t="str">
+        <x:v>Mindful reset, calm solo time</x:v>
+      </x:c>
+      <x:c r="F171" s="4" t="str">
+        <x:v>Plant-forward cafe with a quiet-oriented atmosphere and covered outdoor seating reported.</x:v>
+      </x:c>
+      <x:c r="G171" s="4" t="str">
+        <x:v>₹250–₹850</x:v>
+      </x:c>
+      <x:c r="H171" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I171" s="4" t="str"/>
+      <x:c r="J171" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K171" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Yogisthaan%2C%20Indiranagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L171" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="54" customHeight="1">
+      <x:c r="A172" s="4" t="str">
+        <x:v>White Room Coffee</x:v>
+      </x:c>
+      <x:c r="B172" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C172" s="4" t="str">
+        <x:v>Central Bengaluru (branch verify)</x:v>
+      </x:c>
+      <x:c r="D172" s="4" t="str">
+        <x:v>Coffee stop listed among Bengaluru’s specialty coffee and work cafes.</x:v>
+      </x:c>
+      <x:c r="E172" s="4" t="str">
+        <x:v>Coffee-focused, mellow, simple</x:v>
+      </x:c>
+      <x:c r="F172" s="4" t="str">
+        <x:v>Specific ambience and amenities need branch-level confirmation.</x:v>
+      </x:c>
+      <x:c r="G172" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H172" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I172" s="4" t="str"/>
+      <x:c r="J172" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K172" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=White%20Room%20Coffee%2C%20Central%20Bengaluru%20(branch%20verify)%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L172" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="54" customHeight="1">
+      <x:c r="A173" s="4" t="str">
+        <x:v>Muziris Cafe</x:v>
+      </x:c>
+      <x:c r="B173" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C173" s="4" t="str">
+        <x:v>Bengaluru (branch verify)</x:v>
+      </x:c>
+      <x:c r="D173" s="4" t="str">
+        <x:v>Cafe listed in the Bengaluru specialty-coffee guide.</x:v>
+      </x:c>
+      <x:c r="E173" s="4" t="str">
+        <x:v>Low-key, curious, coffee break</x:v>
+      </x:c>
+      <x:c r="F173" s="4" t="str">
+        <x:v>Vibe and location need current venue confirmation.</x:v>
+      </x:c>
+      <x:c r="G173" s="4" t="str">
+        <x:v>₹250–₹900</x:v>
+      </x:c>
+      <x:c r="H173" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I173" s="4" t="str"/>
+      <x:c r="J173" s="4" t="str">
+        <x:v>https://indiago.app/en/bengaluru/cafes/</x:v>
+      </x:c>
+      <x:c r="K173" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Muziris%20Cafe%2C%20Bengaluru%20(branch%20verify)%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L173" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="54" customHeight="1">
+      <x:c r="A174" s="4" t="str">
+        <x:v>Cafe Plume</x:v>
+      </x:c>
+      <x:c r="B174" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C174" s="4" t="str">
+        <x:v>Indiranagar</x:v>
+      </x:c>
+      <x:c r="D174" s="4" t="str">
+        <x:v>Small cafe repeatedly described by local visitors as cozy.</x:v>
+      </x:c>
+      <x:c r="E174" s="4" t="str">
+        <x:v>Cozy, intimate, low-key</x:v>
+      </x:c>
+      <x:c r="F174" s="4" t="str">
+        <x:v>Cozy-corner cue is community-reported; verify current location and seating.</x:v>
+      </x:c>
+      <x:c r="G174" s="4" t="str">
+        <x:v>₹250–₹850</x:v>
+      </x:c>
+      <x:c r="H174" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I174" s="4" t="str"/>
+      <x:c r="J174" s="4" t="str">
+        <x:v>https://cafeblr.com/</x:v>
+      </x:c>
+      <x:c r="K174" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Plume%2C%20Indiranagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L174" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="54" customHeight="1">
+      <x:c r="A175" s="4" t="str">
+        <x:v>Cafe Hustle</x:v>
+      </x:c>
+      <x:c r="B175" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C175" s="4" t="str">
+        <x:v>HSR Layout</x:v>
+      </x:c>
+      <x:c r="D175" s="4" t="str">
+        <x:v>Neighbourhood cafe with food and coffee, surfaced in local cafe directories.</x:v>
+      </x:c>
+      <x:c r="E175" s="4" t="str">
+        <x:v>Casual, familiar, work break</x:v>
+      </x:c>
+      <x:c r="F175" s="4" t="str">
+        <x:v>Work-friendliness is uncertain; check crowd and outlet access.</x:v>
+      </x:c>
+      <x:c r="G175" s="4" t="str">
+        <x:v>₹200–₹700</x:v>
+      </x:c>
+      <x:c r="H175" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I175" s="4" t="str"/>
+      <x:c r="J175" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K175" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Hustle%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L175" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="54" customHeight="1">
+      <x:c r="A176" s="4" t="str">
+        <x:v>North Star Café</x:v>
+      </x:c>
+      <x:c r="B176" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C176" s="4" t="str">
+        <x:v>HSR Layout</x:v>
+      </x:c>
+      <x:c r="D176" s="4" t="str">
+        <x:v>Neighbourhood cafe for coffee and casual meals.</x:v>
+      </x:c>
+      <x:c r="E176" s="4" t="str">
+        <x:v>Simple, relaxed, easygoing</x:v>
+      </x:c>
+      <x:c r="F176" s="4" t="str">
+        <x:v>Directory-listed cafe; ambience needs a current branch check.</x:v>
+      </x:c>
+      <x:c r="G176" s="4" t="str">
+        <x:v>₹200–₹700</x:v>
+      </x:c>
+      <x:c r="H176" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I176" s="4" t="str"/>
+      <x:c r="J176" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K176" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=North%20Star%20Caf%C3%A9%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L176" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="54" customHeight="1">
+      <x:c r="A177" s="4" t="str">
+        <x:v>Nivys Resto Cafe &amp; Garden Centre</x:v>
+      </x:c>
+      <x:c r="B177" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C177" s="4" t="str">
+        <x:v>Haralur</x:v>
+      </x:c>
+      <x:c r="D177" s="4" t="str">
+        <x:v>Cafe and garden-centre combination for a greener meal stop.</x:v>
+      </x:c>
+      <x:c r="E177" s="4" t="str">
+        <x:v>Leafy, relaxed, nature break</x:v>
+      </x:c>
+      <x:c r="F177" s="4" t="str">
+        <x:v>Garden-centre setting is suggested by the venue listing; verify current outdoor seating.</x:v>
+      </x:c>
+      <x:c r="G177" s="4" t="str">
+        <x:v>₹250–₹900</x:v>
+      </x:c>
+      <x:c r="H177" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I177" s="4" t="str"/>
+      <x:c r="J177" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K177" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Nivys%20Resto%20Cafe%20%26%20Garden%20Centre%2C%20Haralur%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L177" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="54" customHeight="1">
+      <x:c r="A178" s="4" t="str">
+        <x:v>Café Memoire</x:v>
+      </x:c>
+      <x:c r="B178" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C178" s="4" t="str">
+        <x:v>Hulimavu</x:v>
+      </x:c>
+      <x:c r="D178" s="4" t="str">
+        <x:v>Neighbourhood cafe in south Bengaluru for a casual coffee or meal.</x:v>
+      </x:c>
+      <x:c r="E178" s="4" t="str">
+        <x:v>Cozy, quiet break, local</x:v>
+      </x:c>
+      <x:c r="F178" s="4" t="str">
+        <x:v>Vibe is not independently confirmed; visit off-peak and assess on arrival.</x:v>
+      </x:c>
+      <x:c r="G178" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H178" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I178" s="4" t="str"/>
+      <x:c r="J178" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K178" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Caf%C3%A9%20Memoire%2C%20Hulimavu%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L178" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="54" customHeight="1">
+      <x:c r="A179" s="4" t="str">
+        <x:v>Café du L’Amour</x:v>
+      </x:c>
+      <x:c r="B179" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C179" s="4" t="str">
+        <x:v>Koramangala</x:v>
+      </x:c>
+      <x:c r="D179" s="4" t="str">
+        <x:v>Cafe listed in local Bengaluru cafe directory.</x:v>
+      </x:c>
+      <x:c r="E179" s="4" t="str">
+        <x:v>Cozy, date-friendly, catch-up</x:v>
+      </x:c>
+      <x:c r="F179" s="4" t="str">
+        <x:v>Ambience is a discovery cue only; confirm current branch and crowd.</x:v>
+      </x:c>
+      <x:c r="G179" s="4" t="str">
+        <x:v>₹250–₹900</x:v>
+      </x:c>
+      <x:c r="H179" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I179" s="4" t="str"/>
+      <x:c r="J179" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K179" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Caf%C3%A9%20du%20L%E2%80%99Amour%2C%20Koramangala%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L179" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="54" customHeight="1">
+      <x:c r="A180" s="4" t="str">
+        <x:v>Story Coffee</x:v>
+      </x:c>
+      <x:c r="B180" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C180" s="4" t="str">
+        <x:v>Kammanahalli</x:v>
+      </x:c>
+      <x:c r="D180" s="4" t="str">
+        <x:v>Neighbourhood coffee shop and cafe.</x:v>
+      </x:c>
+      <x:c r="E180" s="4" t="str">
+        <x:v>Simple, local, slow sip</x:v>
+      </x:c>
+      <x:c r="F180" s="4" t="str">
+        <x:v>Exact seating/noise details need a current check.</x:v>
+      </x:c>
+      <x:c r="G180" s="4" t="str">
+        <x:v>₹150–₹650</x:v>
+      </x:c>
+      <x:c r="H180" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I180" s="4" t="str"/>
+      <x:c r="J180" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K180" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Story%20Coffee%2C%20Kammanahalli%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L180" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="54" customHeight="1">
+      <x:c r="A181" s="4" t="str">
+        <x:v>Cafe Rome</x:v>
+      </x:c>
+      <x:c r="B181" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C181" s="4" t="str">
+        <x:v>Sahakarnagar</x:v>
+      </x:c>
+      <x:c r="D181" s="4" t="str">
+        <x:v>Cafe listed in north Bengaluru directory results.</x:v>
+      </x:c>
+      <x:c r="E181" s="4" t="str">
+        <x:v>Casual, relaxed, coffee break</x:v>
+      </x:c>
+      <x:c r="F181" s="4" t="str">
+        <x:v>Verify current address, menu and seating before visiting.</x:v>
+      </x:c>
+      <x:c r="G181" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H181" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I181" s="4" t="str"/>
+      <x:c r="J181" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K181" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Rome%2C%20Sahakarnagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L181" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="54" customHeight="1">
+      <x:c r="A182" s="4" t="str">
+        <x:v>Cafe Palmyra</x:v>
+      </x:c>
+      <x:c r="B182" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C182" s="4" t="str">
+        <x:v>Whitefield</x:v>
+      </x:c>
+      <x:c r="D182" s="4" t="str">
+        <x:v>Cafe in the Whitefield area for a sit-down meal or coffee.</x:v>
+      </x:c>
+      <x:c r="E182" s="4" t="str">
+        <x:v>Green, leisurely, catch-up</x:v>
+      </x:c>
+      <x:c r="F182" s="4" t="str">
+        <x:v>Ambience and current operation should be checked.</x:v>
+      </x:c>
+      <x:c r="G182" s="4" t="str">
+        <x:v>₹300–₹1,000</x:v>
+      </x:c>
+      <x:c r="H182" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I182" s="4" t="str"/>
+      <x:c r="J182" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K182" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Palmyra%2C%20Whitefield%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L182" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="54" customHeight="1">
+      <x:c r="A183" s="4" t="str">
+        <x:v>Iris Café &amp; Kitchen</x:v>
+      </x:c>
+      <x:c r="B183" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C183" s="4" t="str">
+        <x:v>JP Nagar</x:v>
+      </x:c>
+      <x:c r="D183" s="4" t="str">
+        <x:v>Cafe and kitchen in JP Nagar with a broad casual menu.</x:v>
+      </x:c>
+      <x:c r="E183" s="4" t="str">
+        <x:v>Easygoing, brunch, conversation</x:v>
+      </x:c>
+      <x:c r="F183" s="4" t="str">
+        <x:v>Meal-led cafe; quieter at off-peak times.</x:v>
+      </x:c>
+      <x:c r="G183" s="4" t="str">
+        <x:v>₹300–₹1,000</x:v>
+      </x:c>
+      <x:c r="H183" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I183" s="4" t="str"/>
+      <x:c r="J183" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K183" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Iris%20Caf%C3%A9%20%26%20Kitchen%2C%20JP%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L183" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="54" customHeight="1">
+      <x:c r="A184" s="4" t="str">
+        <x:v>Café Here &amp; Now</x:v>
+      </x:c>
+      <x:c r="B184" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C184" s="4" t="str">
+        <x:v>HSR Layout</x:v>
+      </x:c>
+      <x:c r="D184" s="4" t="str">
+        <x:v>Cafe listed in HSR for coffee and casual meals.</x:v>
+      </x:c>
+      <x:c r="E184" s="4" t="str">
+        <x:v>Everyday, easygoing, work break</x:v>
+      </x:c>
+      <x:c r="F184" s="4" t="str">
+        <x:v>Confirm laptop rules, sockets and current crowd.</x:v>
+      </x:c>
+      <x:c r="G184" s="4" t="str">
+        <x:v>₹250–₹900</x:v>
+      </x:c>
+      <x:c r="H184" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I184" s="4" t="str"/>
+      <x:c r="J184" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K184" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Caf%C3%A9%20Here%20%26%20Now%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L184" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="54" customHeight="1">
+      <x:c r="A185" s="4" t="str">
+        <x:v>Cuppa Redefined</x:v>
+      </x:c>
+      <x:c r="B185" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C185" s="4" t="str">
+        <x:v>HSR Layout</x:v>
+      </x:c>
+      <x:c r="D185" s="4" t="str">
+        <x:v>Neighbourhood cafe and restaurant with coffee, tea and meals.</x:v>
+      </x:c>
+      <x:c r="E185" s="4" t="str">
+        <x:v>Comfort, casual catch-up</x:v>
+      </x:c>
+      <x:c r="F185" s="4" t="str">
+        <x:v>Restaurant-cafe format; not necessarily quiet during meal times.</x:v>
+      </x:c>
+      <x:c r="G185" s="4" t="str">
+        <x:v>₹250–₹900</x:v>
+      </x:c>
+      <x:c r="H185" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I185" s="4" t="str"/>
+      <x:c r="J185" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K185" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cuppa%20Redefined%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L185" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="54" customHeight="1">
+      <x:c r="A186" s="4" t="str">
+        <x:v>Cafe 60 Four</x:v>
+      </x:c>
+      <x:c r="B186" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C186" s="4" t="str">
+        <x:v>Yelahanka New Town</x:v>
+      </x:c>
+      <x:c r="D186" s="4" t="str">
+        <x:v>Neighbourhood cafe in north Bengaluru.</x:v>
+      </x:c>
+      <x:c r="E186" s="4" t="str">
+        <x:v>Simple, local, slow break</x:v>
+      </x:c>
+      <x:c r="F186" s="4" t="str">
+        <x:v>Verify opening status, exact branch and seating.</x:v>
+      </x:c>
+      <x:c r="G186" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H186" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I186" s="4" t="str"/>
+      <x:c r="J186" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K186" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%2060%20Four%2C%20Yelahanka%20New%20Town%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L186" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="54" customHeight="1">
+      <x:c r="A187" s="4" t="str">
+        <x:v>HSR Sector 7 Café</x:v>
+      </x:c>
+      <x:c r="B187" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C187" s="4" t="str">
+        <x:v>HSR Layout, Sector 7</x:v>
+      </x:c>
+      <x:c r="D187" s="4" t="str">
+        <x:v>Small-area cafe listing for a casual coffee and snack stop.</x:v>
+      </x:c>
+      <x:c r="E187" s="4" t="str">
+        <x:v>Low-key, local, quick coffee</x:v>
+      </x:c>
+      <x:c r="F187" s="4" t="str">
+        <x:v>Generic directory listing; verify exact business name and current address.</x:v>
+      </x:c>
+      <x:c r="G187" s="4" t="str">
+        <x:v>₹150–₹650</x:v>
+      </x:c>
+      <x:c r="H187" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I187" s="4" t="str"/>
+      <x:c r="J187" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K187" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=HSR%20Sector%207%20Caf%C3%A9%2C%20HSR%20Layout%2C%20Sector%207%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L187" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="54" customHeight="1">
+      <x:c r="A188" s="4" t="str">
+        <x:v>Café Nosh</x:v>
+      </x:c>
+      <x:c r="B188" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C188" s="4" t="str">
+        <x:v>Kodigehalli</x:v>
+      </x:c>
+      <x:c r="D188" s="4" t="str">
+        <x:v>Neighbourhood cafe for coffee and casual food in north Bengaluru.</x:v>
+      </x:c>
+      <x:c r="E188" s="4" t="str">
+        <x:v>Casual, familiar, relaxed</x:v>
+      </x:c>
+      <x:c r="F188" s="4" t="str">
+        <x:v>Current seating and operating status need direct confirmation.</x:v>
+      </x:c>
+      <x:c r="G188" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H188" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I188" s="4" t="str"/>
+      <x:c r="J188" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K188" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Caf%C3%A9%20Nosh%2C%20Kodigehalli%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L188" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="54" customHeight="1">
+      <x:c r="A189" s="4" t="str">
+        <x:v>Cafe Kaffea</x:v>
+      </x:c>
+      <x:c r="B189" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C189" s="4" t="str">
+        <x:v>Chandra Layout</x:v>
+      </x:c>
+      <x:c r="D189" s="4" t="str">
+        <x:v>Local cafe in west Bengaluru for a simple snack or coffee visit.</x:v>
+      </x:c>
+      <x:c r="E189" s="4" t="str">
+        <x:v>Simple, budget-aware, local</x:v>
+      </x:c>
+      <x:c r="F189" s="4" t="str">
+        <x:v>Vibe is unverified; check current listing and seating.</x:v>
+      </x:c>
+      <x:c r="G189" s="4" t="str">
+        <x:v>₹150–₹650</x:v>
+      </x:c>
+      <x:c r="H189" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I189" s="4" t="str"/>
+      <x:c r="J189" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K189" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Kaffea%2C%20Chandra%20Layout%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L189" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="54" customHeight="1">
+      <x:c r="A190" s="4" t="str">
+        <x:v>Cafe Down The Alley</x:v>
+      </x:c>
+      <x:c r="B190" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C190" s="4" t="str">
+        <x:v>Hosakerehalli</x:v>
+      </x:c>
+      <x:c r="D190" s="4" t="str">
+        <x:v>Neighbourhood cafe in the southwest part of Bengaluru.</x:v>
+      </x:c>
+      <x:c r="E190" s="4" t="str">
+        <x:v>Cozy, hidden-away, casual</x:v>
+      </x:c>
+      <x:c r="F190" s="4" t="str">
+        <x:v>Alley/neighbourhood feel inferred from name and area; verify in person.</x:v>
+      </x:c>
+      <x:c r="G190" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H190" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I190" s="4" t="str"/>
+      <x:c r="J190" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K190" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cafe%20Down%20The%20Alley%2C%20Hosakerehalli%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L190" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="54" customHeight="1">
+      <x:c r="A191" s="4" t="str">
+        <x:v>The Bangalore Cafe</x:v>
+      </x:c>
+      <x:c r="B191" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C191" s="4" t="str">
+        <x:v>Shanti Nagar</x:v>
+      </x:c>
+      <x:c r="D191" s="4" t="str">
+        <x:v>Cafe listed for central Bengaluru with a casual menu.</x:v>
+      </x:c>
+      <x:c r="E191" s="4" t="str">
+        <x:v>Casual, familiar, easy pause</x:v>
+      </x:c>
+      <x:c r="F191" s="4" t="str">
+        <x:v>Current exact location and atmosphere need a check.</x:v>
+      </x:c>
+      <x:c r="G191" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H191" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I191" s="4" t="str"/>
+      <x:c r="J191" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K191" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Bangalore%20Cafe%2C%20Shanti%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L191" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="54" customHeight="1">
+      <x:c r="A192" s="4" t="str">
+        <x:v>The Hebbal Café</x:v>
+      </x:c>
+      <x:c r="B192" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C192" s="4" t="str">
+        <x:v>Hebbal / Nagavara</x:v>
+      </x:c>
+      <x:c r="D192" s="4" t="str">
+        <x:v>North Bengaluru cafe for a quick meal or coffee stop.</x:v>
+      </x:c>
+      <x:c r="E192" s="4" t="str">
+        <x:v>Simple, local, travel break</x:v>
+      </x:c>
+      <x:c r="F192" s="4" t="str">
+        <x:v>Check branch and traffic-side ambience before visiting.</x:v>
+      </x:c>
+      <x:c r="G192" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H192" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I192" s="4" t="str"/>
+      <x:c r="J192" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K192" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Hebbal%20Caf%C3%A9%2C%20Hebbal%20%2F%20Nagavara%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L192" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="54" customHeight="1">
+      <x:c r="A193" s="4" t="str">
+        <x:v>SLAY Coffee Bar</x:v>
+      </x:c>
+      <x:c r="B193" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C193" s="4" t="str">
+        <x:v>Whitefield</x:v>
+      </x:c>
+      <x:c r="D193" s="4" t="str">
+        <x:v>Coffee bar in Whitefield for a quick specialty-coffee stop.</x:v>
+      </x:c>
+      <x:c r="E193" s="4" t="str">
+        <x:v>Quick coffee, focused, modern</x:v>
+      </x:c>
+      <x:c r="F193" s="4" t="str">
+        <x:v>Coffee-bar format; likely better for a short pause than a long stay.</x:v>
+      </x:c>
+      <x:c r="G193" s="4" t="str">
+        <x:v>₹150–₹600</x:v>
+      </x:c>
+      <x:c r="H193" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I193" s="4" t="str"/>
+      <x:c r="J193" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K193" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=SLAY%20Coffee%20Bar%2C%20Whitefield%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L193" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="54" customHeight="1">
+      <x:c r="A194" s="4" t="str">
+        <x:v>Coffee Confessions</x:v>
+      </x:c>
+      <x:c r="B194" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C194" s="4" t="str">
+        <x:v>Electronic City</x:v>
+      </x:c>
+      <x:c r="D194" s="4" t="str">
+        <x:v>Cafe in Electronic City for coffee and casual meals.</x:v>
+      </x:c>
+      <x:c r="E194" s="4" t="str">
+        <x:v>Low-key, work break, neighborhood</x:v>
+      </x:c>
+      <x:c r="F194" s="4" t="str">
+        <x:v>Verify current venue and laptop amenities.</x:v>
+      </x:c>
+      <x:c r="G194" s="4" t="str">
+        <x:v>₹200–₹800</x:v>
+      </x:c>
+      <x:c r="H194" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I194" s="4" t="str"/>
+      <x:c r="J194" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K194" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Coffee%20Confessions%2C%20Electronic%20City%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L194" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="54" customHeight="1">
+      <x:c r="A195" s="4" t="str">
+        <x:v>Olive Street Food Cafe</x:v>
+      </x:c>
+      <x:c r="B195" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C195" s="4" t="str">
+        <x:v>HSR Layout</x:v>
+      </x:c>
+      <x:c r="D195" s="4" t="str">
+        <x:v>Casual cafe and street-food-style menu option.</x:v>
+      </x:c>
+      <x:c r="E195" s="4" t="str">
+        <x:v>Lively, casual, snack-focused</x:v>
+      </x:c>
+      <x:c r="F195" s="4" t="str">
+        <x:v>Food-led cafe; quieter off-peak, but not a guaranteed calm workspace.</x:v>
+      </x:c>
+      <x:c r="G195" s="4" t="str">
+        <x:v>₹150–₹700</x:v>
+      </x:c>
+      <x:c r="H195" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I195" s="4" t="str"/>
+      <x:c r="J195" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K195" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Olive%20Street%20Food%20Cafe%2C%20HSR%20Layout%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L195" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="54" customHeight="1">
+      <x:c r="A196" s="4" t="str">
+        <x:v>Makkah Cafe</x:v>
+      </x:c>
+      <x:c r="B196" s="4" t="str">
+        <x:v>Cafés &amp; Bakeries</x:v>
+      </x:c>
+      <x:c r="C196" s="4" t="str">
+        <x:v>Richmond Town</x:v>
+      </x:c>
+      <x:c r="D196" s="4" t="str">
+        <x:v>Local cafe/restaurant in Richmond Town for a casual meal.</x:v>
+      </x:c>
+      <x:c r="E196" s="4" t="str">
+        <x:v>Everyday, food-first, local</x:v>
+      </x:c>
+      <x:c r="F196" s="4" t="str">
+        <x:v>Directory-listed; verify exact venue category, current operation and seating.</x:v>
+      </x:c>
+      <x:c r="G196" s="4" t="str">
+        <x:v>₹150–₹700</x:v>
+      </x:c>
+      <x:c r="H196" s="4" t="str">
+        <x:v>Broad per-person estimate; not a checked current menu price. For cafes focused on coffee/snacks, spend may be lower; confirm before visiting.</x:v>
+      </x:c>
+      <x:c r="I196" s="4" t="str"/>
+      <x:c r="J196" s="4" t="str">
+        <x:v>https://bestofbengaluru.com/cafe/</x:v>
+      </x:c>
+      <x:c r="K196" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Makkah%20Cafe%2C%20Richmond%20Town%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L196" s="4" t="str">
+        <x:v>Candidate — verify exact branch, current operation, hours, prices, quiet/laptop rules and seating before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="54" customHeight="1">
+      <x:c r="A197" s="4" t="str">
+        <x:v>PLaY Arena</x:v>
+      </x:c>
+      <x:c r="B197" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C197" s="4" t="str">
+        <x:v>Kasavanahalli / Sarjapur Road</x:v>
+      </x:c>
+      <x:c r="D197" s="4" t="str">
+        <x:v>Multi-activity venue with go-karting, bowling, paintball, climbing and other games.</x:v>
+      </x:c>
+      <x:c r="E197" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F197" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G197" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H197" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I197" s="4" t="str"/>
+      <x:c r="J197" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K197" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=PLaY%20Arena%2C%20Kasavanahalli%20%2F%20Sarjapur%20Road%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L197" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="54" customHeight="1">
+      <x:c r="A198" s="4" t="str">
+        <x:v>Torq03</x:v>
+      </x:c>
+      <x:c r="B198" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C198" s="4" t="str">
+        <x:v>Marathahalli</x:v>
+      </x:c>
+      <x:c r="D198" s="4" t="str">
+        <x:v>Entertainment venue with bowling and indoor games; check current activity lineup.</x:v>
+      </x:c>
+      <x:c r="E198" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F198" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G198" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H198" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I198" s="4" t="str"/>
+      <x:c r="J198" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K198" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Torq03%2C%20Marathahalli%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L198" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="54" customHeight="1">
+      <x:c r="A199" s="4" t="str">
+        <x:v>Loco Bear</x:v>
+      </x:c>
+      <x:c r="B199" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C199" s="4" t="str">
+        <x:v>Koramangala</x:v>
+      </x:c>
+      <x:c r="D199" s="4" t="str">
+        <x:v>Indoor entertainment hub with bowling and games; verify current activities and timings.</x:v>
+      </x:c>
+      <x:c r="E199" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F199" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G199" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H199" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I199" s="4" t="str"/>
+      <x:c r="J199" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K199" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Loco%20Bear%2C%20Koramangala%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L199" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="54" customHeight="1">
+      <x:c r="A200" s="4" t="str">
+        <x:v>The Grid</x:v>
+      </x:c>
+      <x:c r="B200" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C200" s="4" t="str">
+        <x:v>Koramangala</x:v>
+      </x:c>
+      <x:c r="D200" s="4" t="str">
+        <x:v>Gaming arena offering bowling, laser tag and VR-style group activities.</x:v>
+      </x:c>
+      <x:c r="E200" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F200" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G200" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H200" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I200" s="4" t="str"/>
+      <x:c r="J200" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K200" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Grid%2C%20Koramangala%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L200" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="54" customHeight="1">
+      <x:c r="A201" s="4" t="str">
+        <x:v>Amoeba</x:v>
+      </x:c>
+      <x:c r="B201" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C201" s="4" t="str">
+        <x:v>Brigade Road / branches</x:v>
+      </x:c>
+      <x:c r="D201" s="4" t="str">
+        <x:v>Bowling and arcade games in a mall setting; branch offerings vary.</x:v>
+      </x:c>
+      <x:c r="E201" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F201" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G201" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H201" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I201" s="4" t="str"/>
+      <x:c r="J201" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K201" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Amoeba%2C%20Brigade%20Road%20%2F%20branches%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L201" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="54" customHeight="1">
+      <x:c r="A202" s="4" t="str">
+        <x:v>Smaaash</x:v>
+      </x:c>
+      <x:c r="B202" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C202" s="4" t="str">
+        <x:v>Phoenix Marketcity / branch to confirm</x:v>
+      </x:c>
+      <x:c r="D202" s="4" t="str">
+        <x:v>Arcade and simulation games; confirm current Bengaluru location and activities.</x:v>
+      </x:c>
+      <x:c r="E202" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F202" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G202" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H202" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I202" s="4" t="str"/>
+      <x:c r="J202" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K202" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Smaaash%2C%20Phoenix%20Marketcity%20%2F%20branch%20to%20confirm%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L202" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="54" customHeight="1">
+      <x:c r="A203" s="4" t="str">
+        <x:v>Snow City</x:v>
+      </x:c>
+      <x:c r="B203" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C203" s="4" t="str">
+        <x:v>Jayamahal</x:v>
+      </x:c>
+      <x:c r="D203" s="4" t="str">
+        <x:v>Indoor snow park experience; check sessions, clothing rules and current ticket packages.</x:v>
+      </x:c>
+      <x:c r="E203" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F203" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G203" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H203" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I203" s="4" t="str"/>
+      <x:c r="J203" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K203" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Snow%20City%2C%20Jayamahal%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L203" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="54" customHeight="1">
+      <x:c r="A204" s="4" t="str">
+        <x:v>Wonderla Bengaluru</x:v>
+      </x:c>
+      <x:c r="B204" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C204" s="4" t="str">
+        <x:v>Mysore Road outskirts</x:v>
+      </x:c>
+      <x:c r="D204" s="4" t="str">
+        <x:v>Large amusement and water park with rides; plan for a full day and check ticket calendar.</x:v>
+      </x:c>
+      <x:c r="E204" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F204" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G204" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H204" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I204" s="4" t="str"/>
+      <x:c r="J204" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K204" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Wonderla%20Bengaluru%2C%20Mysore%20Road%20outskirts%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L204" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="54" customHeight="1">
+      <x:c r="A205" s="4" t="str">
+        <x:v>Climb Central Bengaluru</x:v>
+      </x:c>
+      <x:c r="B205" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C205" s="4" t="str">
+        <x:v>Marathahalli</x:v>
+      </x:c>
+      <x:c r="D205" s="4" t="str">
+        <x:v>Indoor climbing gym for bouldering and rope climbing; check induction requirements.</x:v>
+      </x:c>
+      <x:c r="E205" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F205" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G205" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H205" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I205" s="4" t="str"/>
+      <x:c r="J205" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K205" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Climb%20Central%20Bengaluru%2C%20Marathahalli%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L205" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="54" customHeight="1">
+      <x:c r="A206" s="4" t="str">
+        <x:v>Equilibrium Climbing Station</x:v>
+      </x:c>
+      <x:c r="B206" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C206" s="4" t="str">
+        <x:v>Indiranagar</x:v>
+      </x:c>
+      <x:c r="D206" s="4" t="str">
+        <x:v>Indoor climbing option for a focused active session; confirm opening status and booking.</x:v>
+      </x:c>
+      <x:c r="E206" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F206" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G206" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H206" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I206" s="4" t="str"/>
+      <x:c r="J206" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K206" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Equilibrium%20Climbing%20Station%2C%20Indiranagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L206" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="54" customHeight="1">
+      <x:c r="A207" s="4" t="str">
+        <x:v>Xtreme Zone</x:v>
+      </x:c>
+      <x:c r="B207" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C207" s="4" t="str">
+        <x:v>Yelahanka / branch to confirm</x:v>
+      </x:c>
+      <x:c r="D207" s="4" t="str">
+        <x:v>Adventure activity operator candidate; verify current site and activity availability.</x:v>
+      </x:c>
+      <x:c r="E207" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F207" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G207" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H207" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I207" s="4" t="str"/>
+      <x:c r="J207" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K207" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Xtreme%20Zone%2C%20Yelahanka%20%2F%20branch%20to%20confirm%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L207" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="54" customHeight="1">
+      <x:c r="A208" s="4" t="str">
+        <x:v>Flying Fox Adventure Park</x:v>
+      </x:c>
+      <x:c r="B208" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C208" s="4" t="str">
+        <x:v>Bannerghatta Road outskirts</x:v>
+      </x:c>
+      <x:c r="D208" s="4" t="str">
+        <x:v>Outdoor adventure experiences such as ropes and zipline-style activities; confirm operations.</x:v>
+      </x:c>
+      <x:c r="E208" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F208" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G208" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H208" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I208" s="4" t="str"/>
+      <x:c r="J208" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K208" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Flying%20Fox%20Adventure%20Park%2C%20Bannerghatta%20Road%20outskirts%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L208" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="54" customHeight="1">
+      <x:c r="A209" s="4" t="str">
+        <x:v>Area 83</x:v>
+      </x:c>
+      <x:c r="B209" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C209" s="4" t="str">
+        <x:v>Ramanagara outskirts</x:v>
+      </x:c>
+      <x:c r="D209" s="4" t="str">
+        <x:v>Outdoor adventure resort with activity packages; travel time and bookings need planning.</x:v>
+      </x:c>
+      <x:c r="E209" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F209" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G209" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H209" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I209" s="4" t="str"/>
+      <x:c r="J209" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K209" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Area%2083%2C%20Ramanagara%20outskirts%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L209" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="54" customHeight="1">
+      <x:c r="A210" s="4" t="str">
+        <x:v>Aruani Grid</x:v>
+      </x:c>
+      <x:c r="B210" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C210" s="4" t="str">
+        <x:v>Dommasandra</x:v>
+      </x:c>
+      <x:c r="D210" s="4" t="str">
+        <x:v>Outdoor activity and adventure venue; confirm activity list and availability.</x:v>
+      </x:c>
+      <x:c r="E210" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F210" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G210" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H210" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I210" s="4" t="str"/>
+      <x:c r="J210" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K210" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Aruani%20Grid%2C%20Dommasandra%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L210" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="54" customHeight="1">
+      <x:c r="A211" s="4" t="str">
+        <x:v>Go Kart Race Track, PLaY Arena</x:v>
+      </x:c>
+      <x:c r="B211" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C211" s="4" t="str">
+        <x:v>Kasavanahalli</x:v>
+      </x:c>
+      <x:c r="D211" s="4" t="str">
+        <x:v>Karting option within the PLaY Arena complex; separate activity charges may apply.</x:v>
+      </x:c>
+      <x:c r="E211" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F211" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G211" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H211" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I211" s="4" t="str"/>
+      <x:c r="J211" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K211" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Go%20Kart%20Race%20Track%2C%20PLaY%20Arena%2C%20Kasavanahalli%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L211" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="54" customHeight="1">
+      <x:c r="A212" s="4" t="str">
+        <x:v>Red Riders Gokarting</x:v>
+      </x:c>
+      <x:c r="B212" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C212" s="4" t="str">
+        <x:v>Kodathi</x:v>
+      </x:c>
+      <x:c r="D212" s="4" t="str">
+        <x:v>Go-karting venue candidate on Bengaluru’s southeast edge; verify exact location and hours.</x:v>
+      </x:c>
+      <x:c r="E212" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F212" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G212" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H212" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I212" s="4" t="str"/>
+      <x:c r="J212" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K212" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Red%20Riders%20Gokarting%2C%20Kodathi%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L212" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="54" customHeight="1">
+      <x:c r="A213" s="4" t="str">
+        <x:v>Aladahalli Lake View GoKarting</x:v>
+      </x:c>
+      <x:c r="B213" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C213" s="4" t="str">
+        <x:v>Aladahalli outskirts</x:v>
+      </x:c>
+      <x:c r="D213" s="4" t="str">
+        <x:v>Go-karting listing with an outdoor setting; verify current operation before travelling.</x:v>
+      </x:c>
+      <x:c r="E213" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F213" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G213" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H213" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I213" s="4" t="str"/>
+      <x:c r="J213" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K213" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Aladahalli%20Lake%20View%20GoKarting%2C%20Aladahalli%20outskirts%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L213" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="54" customHeight="1">
+      <x:c r="A214" s="4" t="str">
+        <x:v>Ramanagara rock climbing area</x:v>
+      </x:c>
+      <x:c r="B214" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C214" s="4" t="str">
+        <x:v>Ramanagara outskirts</x:v>
+      </x:c>
+      <x:c r="D214" s="4" t="str">
+        <x:v>Outdoor bouldering and climbing landscape; use a qualified guide and check access/weather.</x:v>
+      </x:c>
+      <x:c r="E214" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F214" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G214" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H214" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I214" s="4" t="str"/>
+      <x:c r="J214" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K214" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ramanagara%20rock%20climbing%20area%2C%20Ramanagara%20outskirts%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L214" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="54" customHeight="1">
+      <x:c r="A215" s="4" t="str">
+        <x:v>Bowling at Phoenix Marketcity</x:v>
+      </x:c>
+      <x:c r="B215" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C215" s="4" t="str">
+        <x:v>Mahadevapura</x:v>
+      </x:c>
+      <x:c r="D215" s="4" t="str">
+        <x:v>Mall-based bowling and arcade session; check operator, lanes and booking slots.</x:v>
+      </x:c>
+      <x:c r="E215" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F215" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G215" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H215" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I215" s="4" t="str"/>
+      <x:c r="J215" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K215" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bowling%20at%20Phoenix%20Marketcity%2C%20Mahadevapura%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L215" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="54" customHeight="1">
+      <x:c r="A216" s="4" t="str">
+        <x:v>Laser tag at PLaY Arena</x:v>
+      </x:c>
+      <x:c r="B216" s="4" t="str">
+        <x:v>Adventure &amp; Games</x:v>
+      </x:c>
+      <x:c r="C216" s="4" t="str">
+        <x:v>Kasavanahalli</x:v>
+      </x:c>
+      <x:c r="D216" s="4" t="str">
+        <x:v>Team laser-tag activity; venue rules and minimum group size may apply.</x:v>
+      </x:c>
+      <x:c r="E216" s="4" t="str">
+        <x:v>Playful, energetic, challenge-seeking</x:v>
+      </x:c>
+      <x:c r="F216" s="4" t="str">
+        <x:v>Active, social and often loud; confirm age, group-size and booking rules</x:v>
+      </x:c>
+      <x:c r="G216" s="4" t="str">
+        <x:v>₹300–₹2,500 per person/activity (broad estimate)</x:v>
+      </x:c>
+      <x:c r="H216" s="4" t="str">
+        <x:v>Indicative activity band only; booking, duration and weekday/weekend pricing differ</x:v>
+      </x:c>
+      <x:c r="I216" s="4" t="str"/>
+      <x:c r="J216" s="4" t="str">
+        <x:v>https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets</x:v>
+      </x:c>
+      <x:c r="K216" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Laser%20tag%20at%20PLaY%20Arena%2C%20Kasavanahalli%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L216" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="54" customHeight="1">
+      <x:c r="A217" s="4" t="str">
+        <x:v>Ranga Shankara</x:v>
+      </x:c>
+      <x:c r="B217" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C217" s="4" t="str">
+        <x:v>JP Nagar</x:v>
+      </x:c>
+      <x:c r="D217" s="4" t="str">
+        <x:v>Respected theatre venue with a steady programme of Kannada and other-language plays.</x:v>
+      </x:c>
+      <x:c r="E217" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F217" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G217" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H217" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I217" s="4" t="str"/>
+      <x:c r="J217" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K217" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ranga%20Shankara%2C%20JP%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L217" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="54" customHeight="1">
+      <x:c r="A218" s="4" t="str">
+        <x:v>Chowdiah Memorial Hall</x:v>
+      </x:c>
+      <x:c r="B218" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C218" s="4" t="str">
+        <x:v>Vyalikaval</x:v>
+      </x:c>
+      <x:c r="D218" s="4" t="str">
+        <x:v>Distinctive violin-shaped auditorium hosting music, dance and public events.</x:v>
+      </x:c>
+      <x:c r="E218" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F218" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G218" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H218" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I218" s="4" t="str"/>
+      <x:c r="J218" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K218" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Chowdiah%20Memorial%20Hall%2C%20Vyalikaval%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L218" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="54" customHeight="1">
+      <x:c r="A219" s="4" t="str">
+        <x:v>Bangalore International Centre</x:v>
+      </x:c>
+      <x:c r="B219" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C219" s="4" t="str">
+        <x:v>Domlur</x:v>
+      </x:c>
+      <x:c r="D219" s="4" t="str">
+        <x:v>Cultural centre for talks, performances, screenings and exhibitions.</x:v>
+      </x:c>
+      <x:c r="E219" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F219" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G219" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H219" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I219" s="4" t="str"/>
+      <x:c r="J219" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K219" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bangalore%20International%20Centre%2C%20Domlur%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L219" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="54" customHeight="1">
+      <x:c r="A220" s="4" t="str">
+        <x:v>Lahe Lahe</x:v>
+      </x:c>
+      <x:c r="B220" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C220" s="4" t="str">
+        <x:v>Indiranagar</x:v>
+      </x:c>
+      <x:c r="D220" s="4" t="str">
+        <x:v>Community arts space for workshops, performances and creative gatherings.</x:v>
+      </x:c>
+      <x:c r="E220" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F220" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G220" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H220" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I220" s="4" t="str"/>
+      <x:c r="J220" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K220" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lahe%20Lahe%2C%20Indiranagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L220" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="54" customHeight="1">
+      <x:c r="A221" s="4" t="str">
+        <x:v>Jagriti Theatre</x:v>
+      </x:c>
+      <x:c r="B221" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C221" s="4" t="str">
+        <x:v>Whitefield</x:v>
+      </x:c>
+      <x:c r="D221" s="4" t="str">
+        <x:v>Theatre venue with plays and cultural programming; check schedule.</x:v>
+      </x:c>
+      <x:c r="E221" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F221" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G221" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H221" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I221" s="4" t="str"/>
+      <x:c r="J221" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K221" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jagriti%20Theatre%2C%20Whitefield%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L221" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="54" customHeight="1">
+      <x:c r="A222" s="4" t="str">
+        <x:v>Alliance Française de Bangalore</x:v>
+      </x:c>
+      <x:c r="B222" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C222" s="4" t="str">
+        <x:v>Vasanth Nagar</x:v>
+      </x:c>
+      <x:c r="D222" s="4" t="str">
+        <x:v>French cultural centre with film, art, language and performance events.</x:v>
+      </x:c>
+      <x:c r="E222" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F222" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G222" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H222" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I222" s="4" t="str"/>
+      <x:c r="J222" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K222" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Alliance%20Fran%C3%A7aise%20de%20Bangalore%2C%20Vasanth%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L222" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="54" customHeight="1">
+      <x:c r="A223" s="4" t="str">
+        <x:v>Goethe-Institut / Max Mueller Bhavan</x:v>
+      </x:c>
+      <x:c r="B223" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C223" s="4" t="str">
+        <x:v>Indiranagar</x:v>
+      </x:c>
+      <x:c r="D223" s="4" t="str">
+        <x:v>German cultural institute with talks, screenings, exhibitions and performances.</x:v>
+      </x:c>
+      <x:c r="E223" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F223" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G223" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H223" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I223" s="4" t="str"/>
+      <x:c r="J223" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K223" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Goethe-Institut%20%2F%20Max%20Mueller%20Bhavan%2C%20Indiranagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L223" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="54" customHeight="1">
+      <x:c r="A224" s="4" t="str">
+        <x:v>Bangalore Gayana Samaja</x:v>
+      </x:c>
+      <x:c r="B224" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C224" s="4" t="str">
+        <x:v>Basavanagudi</x:v>
+      </x:c>
+      <x:c r="D224" s="4" t="str">
+        <x:v>Long-running venue for classical music, dance and cultural performances.</x:v>
+      </x:c>
+      <x:c r="E224" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F224" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G224" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H224" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I224" s="4" t="str"/>
+      <x:c r="J224" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K224" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bangalore%20Gayana%20Samaja%2C%20Basavanagudi%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L224" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="54" customHeight="1">
+      <x:c r="A225" s="4" t="str">
+        <x:v>Karnataka Chitrakala Parishath galleries</x:v>
+      </x:c>
+      <x:c r="B225" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C225" s="4" t="str">
+        <x:v>Kumara Krupa Road</x:v>
+      </x:c>
+      <x:c r="D225" s="4" t="str">
+        <x:v>Gallery campus for exhibitions, folk art and visual-culture events.</x:v>
+      </x:c>
+      <x:c r="E225" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F225" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G225" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H225" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I225" s="4" t="str"/>
+      <x:c r="J225" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K225" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Karnataka%20Chitrakala%20Parishath%20galleries%2C%20Kumara%20Krupa%20Road%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L225" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="54" customHeight="1">
+      <x:c r="A226" s="4" t="str">
+        <x:v>Museum of Art &amp; Photography events</x:v>
+      </x:c>
+      <x:c r="B226" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C226" s="4" t="str">
+        <x:v>Cubbon Road</x:v>
+      </x:c>
+      <x:c r="D226" s="4" t="str">
+        <x:v>Talks, workshops and exhibitions within a contemporary art museum.</x:v>
+      </x:c>
+      <x:c r="E226" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F226" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G226" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H226" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I226" s="4" t="str"/>
+      <x:c r="J226" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K226" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Museum%20of%20Art%20%26%20Photography%20events%2C%20Cubbon%20Road%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L226" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="54" customHeight="1">
+      <x:c r="A227" s="4" t="str">
+        <x:v>National Gallery of Modern Art events</x:v>
+      </x:c>
+      <x:c r="B227" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C227" s="4" t="str">
+        <x:v>Vasanth Nagar</x:v>
+      </x:c>
+      <x:c r="D227" s="4" t="str">
+        <x:v>Exhibitions and cultural programmes in a heritage gallery setting.</x:v>
+      </x:c>
+      <x:c r="E227" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F227" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G227" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H227" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I227" s="4" t="str"/>
+      <x:c r="J227" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K227" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=National%20Gallery%20of%20Modern%20Art%20events%2C%20Vasanth%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L227" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="54" customHeight="1">
+      <x:c r="A228" s="4" t="str">
+        <x:v>Bangalore Creative Circus</x:v>
+      </x:c>
+      <x:c r="B228" s="4" t="str">
+        <x:v>Arts &amp; Performance</x:v>
+      </x:c>
+      <x:c r="C228" s="4" t="str">
+        <x:v>Yeshwanthpur</x:v>
+      </x:c>
+      <x:c r="D228" s="4" t="str">
+        <x:v>Creative and sustainability-focused community campus; public programmes vary.</x:v>
+      </x:c>
+      <x:c r="E228" s="4" t="str">
+        <x:v>Inspired, expressive, immersed</x:v>
+      </x:c>
+      <x:c r="F228" s="4" t="str">
+        <x:v>Programme-led; intimate theatre, gallery or live-event energy</x:v>
+      </x:c>
+      <x:c r="G228" s="4" t="str">
+        <x:v>Free–₹2,000+ depending on event</x:v>
+      </x:c>
+      <x:c r="H228" s="4" t="str">
+        <x:v>Event and exhibition prices change; verify the live calendar</x:v>
+      </x:c>
+      <x:c r="I228" s="4" t="str"/>
+      <x:c r="J228" s="4" t="str">
+        <x:v>https://karnatakatourism.org/wp-content/uploads/2020/05/SYA-Bengaluru-Brochure-English.pdf</x:v>
+      </x:c>
+      <x:c r="K228" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bangalore%20Creative%20Circus%2C%20Yeshwanthpur%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L228" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="54" customHeight="1">
+      <x:c r="A229" s="4" t="str">
+        <x:v>KR Market (City Market)</x:v>
+      </x:c>
+      <x:c r="B229" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C229" s="4" t="str">
+        <x:v>Kalassipalya</x:v>
+      </x:c>
+      <x:c r="D229" s="4" t="str">
+        <x:v>Dense wholesale market known for flowers, produce and early-morning city rhythms.</x:v>
+      </x:c>
+      <x:c r="E229" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F229" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G229" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H229" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I229" s="4" t="str"/>
+      <x:c r="J229" s="4" t="str">
         <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
       </x:c>
-      <x:c r="K166" s="4" t="str">
+      <x:c r="K229" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=KR%20Market%20(City%20Market)%2C%20Kalassipalya%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L229" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="54" customHeight="1">
+      <x:c r="A230" s="4" t="str">
+        <x:v>Commercial Street</x:v>
+      </x:c>
+      <x:c r="B230" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C230" s="4" t="str">
+        <x:v>Tasker Town</x:v>
+      </x:c>
+      <x:c r="D230" s="4" t="str">
+        <x:v>Busy shopping district for clothes, shoes, accessories and street food.</x:v>
+      </x:c>
+      <x:c r="E230" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F230" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G230" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H230" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I230" s="4" t="str"/>
+      <x:c r="J230" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K230" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Commercial%20Street%2C%20Tasker%20Town%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L230" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="54" customHeight="1">
+      <x:c r="A231" s="4" t="str">
+        <x:v>Church Street</x:v>
+      </x:c>
+      <x:c r="B231" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C231" s="4" t="str">
+        <x:v>Central Business District</x:v>
+      </x:c>
+      <x:c r="D231" s="4" t="str">
+        <x:v>Walkable high street with bookstores, cafes and retail.</x:v>
+      </x:c>
+      <x:c r="E231" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F231" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G231" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H231" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I231" s="4" t="str"/>
+      <x:c r="J231" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K231" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Church%20Street%2C%20Central%20Business%20District%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L231" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="54" customHeight="1">
+      <x:c r="A232" s="4" t="str">
+        <x:v>MG Road</x:v>
+      </x:c>
+      <x:c r="B232" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C232" s="4" t="str">
+        <x:v>Central Business District</x:v>
+      </x:c>
+      <x:c r="D232" s="4" t="str">
+        <x:v>Central shopping and transit corridor with retail, dining and city landmarks.</x:v>
+      </x:c>
+      <x:c r="E232" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F232" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G232" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H232" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I232" s="4" t="str"/>
+      <x:c r="J232" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K232" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=MG%20Road%2C%20Central%20Business%20District%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L232" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="54" customHeight="1">
+      <x:c r="A233" s="4" t="str">
+        <x:v>Brigade Road</x:v>
+      </x:c>
+      <x:c r="B233" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C233" s="4" t="str">
+        <x:v>Central Business District</x:v>
+      </x:c>
+      <x:c r="D233" s="4" t="str">
+        <x:v>Lively retail and dining street linking MG Road and Residency Road.</x:v>
+      </x:c>
+      <x:c r="E233" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F233" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G233" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H233" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I233" s="4" t="str"/>
+      <x:c r="J233" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K233" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Brigade%20Road%2C%20Central%20Business%20District%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L233" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="54" customHeight="1">
+      <x:c r="A234" s="4" t="str">
+        <x:v>Jayanagar 4th Block Shopping Complex</x:v>
+      </x:c>
+      <x:c r="B234" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C234" s="4" t="str">
+        <x:v>Jayanagar</x:v>
+      </x:c>
+      <x:c r="D234" s="4" t="str">
+        <x:v>Neighbourhood shopping hub with street stalls, stores and quick eats.</x:v>
+      </x:c>
+      <x:c r="E234" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F234" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G234" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H234" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I234" s="4" t="str"/>
+      <x:c r="J234" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K234" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jayanagar%204th%20Block%20Shopping%20Complex%2C%20Jayanagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L234" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="54" customHeight="1">
+      <x:c r="A235" s="4" t="str">
+        <x:v>Gandhi Bazaar</x:v>
+      </x:c>
+      <x:c r="B235" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C235" s="4" t="str">
+        <x:v>Basavanagudi</x:v>
+      </x:c>
+      <x:c r="D235" s="4" t="str">
+        <x:v>Traditional market street for flowers, produce, sweets and local shopping.</x:v>
+      </x:c>
+      <x:c r="E235" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F235" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G235" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H235" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I235" s="4" t="str"/>
+      <x:c r="J235" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K235" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gandhi%20Bazaar%2C%20Basavanagudi%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L235" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="54" customHeight="1">
+      <x:c r="A236" s="4" t="str">
+        <x:v>Chickpet Market</x:v>
+      </x:c>
+      <x:c r="B236" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C236" s="4" t="str">
+        <x:v>Chickpet</x:v>
+      </x:c>
+      <x:c r="D236" s="4" t="str">
+        <x:v>Wholesale textile and trading district; busy lanes reward unhurried browsing.</x:v>
+      </x:c>
+      <x:c r="E236" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F236" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G236" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H236" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I236" s="4" t="str"/>
+      <x:c r="J236" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K236" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Chickpet%20Market%2C%20Chickpet%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L236" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="54" customHeight="1">
+      <x:c r="A237" s="4" t="str">
+        <x:v>Avenue Road</x:v>
+      </x:c>
+      <x:c r="B237" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C237" s="4" t="str">
+        <x:v>Central Bengaluru</x:v>
+      </x:c>
+      <x:c r="D237" s="4" t="str">
+        <x:v>Bookshops, stationery, paper and old-city trading streets.</x:v>
+      </x:c>
+      <x:c r="E237" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F237" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G237" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H237" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I237" s="4" t="str"/>
+      <x:c r="J237" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K237" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Avenue%20Road%2C%20Central%20Bengaluru%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L237" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="54" customHeight="1">
+      <x:c r="A238" s="4" t="str">
+        <x:v>Russell Market</x:v>
+      </x:c>
+      <x:c r="B238" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C238" s="4" t="str">
+        <x:v>Shivajinagar</x:v>
+      </x:c>
+      <x:c r="D238" s="4" t="str">
+        <x:v>Historic indoor market for produce, meat, flowers and everyday goods.</x:v>
+      </x:c>
+      <x:c r="E238" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F238" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G238" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H238" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I238" s="4" t="str"/>
+      <x:c r="J238" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K238" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Russell%20Market%2C%20Shivajinagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L238" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="54" customHeight="1">
+      <x:c r="A239" s="4" t="str">
+        <x:v>UB City</x:v>
+      </x:c>
+      <x:c r="B239" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C239" s="4" t="str">
+        <x:v>Vittal Mallya Road</x:v>
+      </x:c>
+      <x:c r="D239" s="4" t="str">
+        <x:v>Upscale retail and dining complex with an open-air courtyard.</x:v>
+      </x:c>
+      <x:c r="E239" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F239" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G239" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H239" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I239" s="4" t="str"/>
+      <x:c r="J239" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K239" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=UB%20City%2C%20Vittal%20Mallya%20Road%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L239" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="54" customHeight="1">
+      <x:c r="A240" s="4" t="str">
+        <x:v>Orion Mall</x:v>
+      </x:c>
+      <x:c r="B240" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C240" s="4" t="str">
+        <x:v>Rajajinagar</x:v>
+      </x:c>
+      <x:c r="D240" s="4" t="str">
+        <x:v>Large mall with shopping, dining and entertainment by a lakefront promenade.</x:v>
+      </x:c>
+      <x:c r="E240" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F240" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G240" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H240" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I240" s="4" t="str"/>
+      <x:c r="J240" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K240" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Orion%20Mall%2C%20Rajajinagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L240" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="54" customHeight="1">
+      <x:c r="A241" s="4" t="str">
+        <x:v>Phoenix Marketcity</x:v>
+      </x:c>
+      <x:c r="B241" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C241" s="4" t="str">
+        <x:v>Mahadevapura</x:v>
+      </x:c>
+      <x:c r="D241" s="4" t="str">
+        <x:v>Large retail and entertainment mall on the eastern side of the city.</x:v>
+      </x:c>
+      <x:c r="E241" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F241" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G241" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H241" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I241" s="4" t="str"/>
+      <x:c r="J241" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K241" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Phoenix%20Marketcity%2C%20Mahadevapura%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L241" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="54" customHeight="1">
+      <x:c r="A242" s="4" t="str">
+        <x:v>Mantri Square Mall</x:v>
+      </x:c>
+      <x:c r="B242" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C242" s="4" t="str">
+        <x:v>Malleshwaram</x:v>
+      </x:c>
+      <x:c r="D242" s="4" t="str">
+        <x:v>Transit-connected shopping and entertainment mall.</x:v>
+      </x:c>
+      <x:c r="E242" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F242" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G242" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H242" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I242" s="4" t="str"/>
+      <x:c r="J242" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K242" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Mantri%20Square%20Mall%2C%20Malleshwaram%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L242" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="54" customHeight="1">
+      <x:c r="A243" s="4" t="str">
+        <x:v>Lulu Mall Bengaluru</x:v>
+      </x:c>
+      <x:c r="B243" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C243" s="4" t="str">
+        <x:v>Gopalapura / Mysore Road</x:v>
+      </x:c>
+      <x:c r="D243" s="4" t="str">
+        <x:v>Large mall with retail, food and family entertainment; check current events.</x:v>
+      </x:c>
+      <x:c r="E243" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F243" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G243" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H243" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I243" s="4" t="str"/>
+      <x:c r="J243" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K243" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lulu%20Mall%20Bengaluru%2C%20Gopalapura%20%2F%20Mysore%20Road%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L243" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="54" customHeight="1">
+      <x:c r="A244" s="4" t="str">
+        <x:v>Brigade Orion East</x:v>
+      </x:c>
+      <x:c r="B244" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C244" s="4" t="str">
+        <x:v>Banaswadi</x:v>
+      </x:c>
+      <x:c r="D244" s="4" t="str">
+        <x:v>Neighbourhood mall and dining hub in northeast Bengaluru.</x:v>
+      </x:c>
+      <x:c r="E244" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F244" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G244" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H244" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I244" s="4" t="str"/>
+      <x:c r="J244" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K244" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Brigade%20Orion%20East%2C%20Banaswadi%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L244" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="54" customHeight="1">
+      <x:c r="A245" s="4" t="str">
+        <x:v>Sankey Road design and retail stretch</x:v>
+      </x:c>
+      <x:c r="B245" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C245" s="4" t="str">
+        <x:v>Vasanth Nagar</x:v>
+      </x:c>
+      <x:c r="D245" s="4" t="str">
+        <x:v>Small boutiques and cafes in a leafy central neighbourhood.</x:v>
+      </x:c>
+      <x:c r="E245" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F245" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G245" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H245" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I245" s="4" t="str"/>
+      <x:c r="J245" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K245" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sankey%20Road%20design%20and%20retail%20stretch%2C%20Vasanth%20Nagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L245" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="54" customHeight="1">
+      <x:c r="A246" s="4" t="str">
+        <x:v>National Market</x:v>
+      </x:c>
+      <x:c r="B246" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C246" s="4" t="str">
+        <x:v>Gandhinagar</x:v>
+      </x:c>
+      <x:c r="D246" s="4" t="str">
+        <x:v>Compact electronics and retail market; compare prices and check item warranties.</x:v>
+      </x:c>
+      <x:c r="E246" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F246" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G246" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H246" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I246" s="4" t="str"/>
+      <x:c r="J246" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K246" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=National%20Market%2C%20Gandhinagar%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L246" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="54" customHeight="1">
+      <x:c r="A247" s="4" t="str">
+        <x:v>Malleswaram 8th Cross Market</x:v>
+      </x:c>
+      <x:c r="B247" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C247" s="4" t="str">
+        <x:v>Malleshwaram</x:v>
+      </x:c>
+      <x:c r="D247" s="4" t="str">
+        <x:v>Traditional neighbourhood shopping lane with produce, flowers and snacks.</x:v>
+      </x:c>
+      <x:c r="E247" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F247" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G247" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H247" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I247" s="4" t="str"/>
+      <x:c r="J247" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K247" s="4" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Malleswaram%208th%20Cross%20Market%2C%20Malleshwaram%2C%20Bengaluru</x:v>
+      </x:c>
+      <x:c r="L247" s="4" t="str">
+        <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="54" customHeight="1">
+      <x:c r="A248" s="4" t="str">
+        <x:v>V.V. Puram Thindi Beedi</x:v>
+      </x:c>
+      <x:c r="B248" s="4" t="str">
+        <x:v>Markets &amp; Shopping</x:v>
+      </x:c>
+      <x:c r="C248" s="4" t="str">
+        <x:v>V.V. Puram</x:v>
+      </x:c>
+      <x:c r="D248" s="4" t="str">
+        <x:v>Food-focused street market and evening snack crawl.</x:v>
+      </x:c>
+      <x:c r="E248" s="4" t="str">
+        <x:v>Browse, discover, people-watch</x:v>
+      </x:c>
+      <x:c r="F248" s="4" t="str">
+        <x:v>Lively, sensory and often crowded; weekends and festivals intensify footfall</x:v>
+      </x:c>
+      <x:c r="G248" s="4" t="str">
+        <x:v>No entry fee; shopping spend varies widely</x:v>
+      </x:c>
+      <x:c r="H248" s="4" t="str">
+        <x:v>Entry is generally free; individual purchases are not estimated</x:v>
+      </x:c>
+      <x:c r="I248" s="4" t="str"/>
+      <x:c r="J248" s="4" t="str">
+        <x:v>https://karnatakatourism.org/en/destinations/bengaluru/</x:v>
+      </x:c>
+      <x:c r="K248" s="4" t="str">
         <x:v>https://www.google.com/maps/search/?api=1&amp;query=V.V.%20Puram%20Thindi%20Beedi%2C%20V.V.%20Puram%2C%20Bengaluru</x:v>
       </x:c>
-      <x:c r="L166" s="4" t="str">
+      <x:c r="L248" s="4" t="str">
         <x:v>Candidate — verify current operation, exact branch, hours and prices before publishing</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc353353bffad457f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8b2ffd022554f7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6332,15 +9296,15 @@
         <x:v>Research draft — 27 October 2026</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="42" customHeight="1">
+    <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>Coverage</x:v>
       </x:c>
       <x:c r="B2" s="4" t="str">
-        <x:v>165 candidate places across 8 experience categories. This is a broad starter catalogue, not a complete verified inventory of every Bengaluru venue.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="42" customHeight="1">
+        <x:v>247 candidate places across 8 experience categories, including 107 cafe, coffee-shop and bakery candidates. This is a broad starter catalogue, not a complete verified inventory of every Bengaluru venue.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="11" t="str">
         <x:v>How to use</x:v>
       </x:c>
@@ -6348,7 +9312,7 @@
         <x:v>Use the Places sheet as a human-review catalogue. Blank Qloo entity IDs must be resolved against Qloo before using its entity filter or ranking.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="42" customHeight="1">
+    <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="11" t="str">
         <x:v>Pricing</x:v>
       </x:c>
@@ -6356,15 +9320,15 @@
         <x:v>All prices are indicative category-level bands or entry-fee guidance, not confirmed live tariffs. Check venue ticket pages/menus before publishing or promising a budget.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="42" customHeight="1">
+    <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="11" t="str">
         <x:v>Mood and ambience</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>These are editorial discovery cues inferred from venue type and public descriptions; they are not measured sentiment or guaranteed crowd conditions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+        <x:v>Mood and ambience cues are more specific in the cafe section. Some are sourced from public guides; others are editorial discovery cues. They are not measured sentiment or guarantees about noise, crowd, seating, laptop access or atmosphere. Check the exact branch and time.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="11" t="str">
         <x:v>Verification</x:v>
       </x:c>
@@ -6372,15 +9336,15 @@
         <x:v>Every row is a candidate. Confirm exact branch/location, open status, access rules, hours, age restrictions and current prices before showing it to users.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="88" customHeight="1">
+    <x:row r="7" ht="96" customHeight="1">
       <x:c r="A7" s="11" t="str">
         <x:v>Sources</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>Government of Karnataka Bengaluru tourism: https://bengaluruurban.nic.in/en/tourism/ ; Karnataka Tourism Bengaluru: https://karnatakatourism.org/en/destinations/bengaluru/ ; Karnataka Tourism Paper &amp; Pie: https://karnatakatourism.org/en/experiences/paper-pie-cafe/ ; District PLaY Arena: https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets ; individual venue lookup links are in the Places sheet.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="88" customHeight="1">
+        <x:v>Government of Karnataka Bengaluru tourism: https://bengaluruurban.nic.in/en/tourism/ ; Karnataka Tourism Bengaluru: https://karnatakatourism.org/en/destinations/bengaluru/ ; cafe directory: https://cafeblr.com/ ; Bengaluru specialty coffee and work-cafe guide (facts checked 2 Oct 2026): https://indiago.app/en/bengaluru/cafes/ ; cafe listings: https://bestofbengaluru.com/cafe/ ; Karnataka Tourism Paper &amp; Pie: https://karnatakatourism.org/en/experiences/paper-pie-cafe/ ; District PLaY Arena: https://www.district.in/events/play-arena-bengaluru-2025-buy-tickets ; venue lookup links are included per row.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="11" t="str">
         <x:v>OpenStreetMap</x:v>
       </x:c>
@@ -6388,7 +9352,7 @@
         <x:v>A citywide Overpass query was attempted in the browser, but the result was too large to render reliably. This workbook does not claim to be an OSM export. If OSM data is added later, retain attribution and comply with ODbL.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="42" customHeight="1">
+    <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>Qloo integration</x:v>
       </x:c>
@@ -6396,7 +9360,7 @@
         <x:v>The catalogue establishes canonical category and venue identity. Qloo should supply taste affinity/ranking within the selected category; do not let taste associations relabel a venue as a different place type.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+    <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="11" t="str">
         <x:v>Last researched</x:v>
       </x:c>
